--- a/results/01_pollution_assessment/PCA_Stressors/tables/MaxRel_site_rankings.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/MaxRel_site_rankings.xlsx
@@ -451,11 +451,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4279270434436434</v>
+        <v>-0.4022551669291249</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -467,11 +467,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>004ABC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4315652138063645</v>
+        <v>-0.2280902140263398</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>010B</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4452953699698398</v>
+        <v>-0.1685092747940378</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -499,11 +499,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>026C</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4499061108660709</v>
+        <v>-0.1262227552824805</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -515,11 +515,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4566228460312882</v>
+        <v>0.01017673150811147</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.4643361686496821</v>
+        <v>0.02075406377236158</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4645219119572452</v>
+        <v>0.02202355758647872</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -563,11 +563,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4668088778224345</v>
+        <v>0.03006659771482753</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.467512626807579</v>
+        <v>0.05587728398447637</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.4696021838684143</v>
+        <v>0.05674552872975166</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -611,11 +611,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.4767018754778721</v>
+        <v>0.1831052725646437</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -627,11 +627,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4785962151959065</v>
+        <v>0.1906505373581875</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -643,11 +643,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4816008485980839</v>
+        <v>0.2080320203356396</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
@@ -659,11 +659,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4817703950445548</v>
+        <v>0.2316925153583238</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.482292423318319</v>
+        <v>0.2442386661857714</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -691,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.484952423083475</v>
+        <v>0.2549825368686213</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -707,11 +707,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4852841580118419</v>
+        <v>0.2620814423873599</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -723,11 +723,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4854230154784182</v>
+        <v>0.28106403645769</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -739,11 +739,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>036C</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4917373475281424</v>
+        <v>0.2843845156874721</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -755,11 +755,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>035C</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4920495726049761</v>
+        <v>0.2864756987871691</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
@@ -771,11 +771,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4977908434553533</v>
+        <v>0.2947578242478518</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
@@ -787,11 +787,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>S69</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4986068132440482</v>
+        <v>0.3002658069252208</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
@@ -803,11 +803,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.4996454746195236</v>
+        <v>0.3010141847338035</v>
       </c>
       <c r="D24" t="n">
         <v>23</v>
@@ -819,11 +819,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.4996803849859776</v>
+        <v>0.3017315555677913</v>
       </c>
       <c r="D25" t="n">
         <v>24</v>
@@ -835,11 +835,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>139B</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.5001062400358601</v>
+        <v>0.3020051722514078</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
@@ -851,11 +851,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.5005856599216519</v>
+        <v>0.3135571086324083</v>
       </c>
       <c r="D27" t="n">
         <v>26</v>
@@ -867,11 +867,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.5011199261156756</v>
+        <v>0.3289455898705217</v>
       </c>
       <c r="D28" t="n">
         <v>27</v>
@@ -883,11 +883,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.5024228727994454</v>
+        <v>0.3316121209436056</v>
       </c>
       <c r="D29" t="n">
         <v>28</v>
@@ -899,11 +899,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.5032146687493856</v>
+        <v>0.3327282763969321</v>
       </c>
       <c r="D30" t="n">
         <v>29</v>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.5104225059758862</v>
+        <v>0.3357388722078157</v>
       </c>
       <c r="D31" t="n">
         <v>30</v>
@@ -931,11 +931,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S82</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.5115589970868325</v>
+        <v>0.3593948198147103</v>
       </c>
       <c r="D32" t="n">
         <v>31</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.5127327830639198</v>
+        <v>0.3859934558355891</v>
       </c>
       <c r="D33" t="n">
         <v>32</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>S68</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.5138836760132525</v>
+        <v>0.3952472834481091</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
@@ -979,11 +979,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.5163819878358257</v>
+        <v>0.4202137105699785</v>
       </c>
       <c r="D35" t="n">
         <v>34</v>
@@ -995,11 +995,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.5184533233839834</v>
+        <v>0.4203976788765076</v>
       </c>
       <c r="D36" t="n">
         <v>35</v>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.5186062015990544</v>
+        <v>0.4546077021090476</v>
       </c>
       <c r="D37" t="n">
         <v>36</v>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t xml:space="preserve">111C </t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.5203593278017669</v>
+        <v>0.4712671734293135</v>
       </c>
       <c r="D38" t="n">
         <v>37</v>
@@ -1043,11 +1043,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.5209571937133598</v>
+        <v>0.4825169087612939</v>
       </c>
       <c r="D39" t="n">
         <v>38</v>
@@ -1059,11 +1059,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.5217034781906107</v>
+        <v>0.5202305328356266</v>
       </c>
       <c r="D40" t="n">
         <v>39</v>
@@ -1075,11 +1075,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.5227822636279221</v>
+        <v>0.5325111195530996</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.5228091805623424</v>
+        <v>0.5522479520124634</v>
       </c>
       <c r="D42" t="n">
         <v>41</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.5234719288435601</v>
+        <v>0.5942638348690173</v>
       </c>
       <c r="D43" t="n">
         <v>42</v>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>S74</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.5254974249028412</v>
+        <v>0.599459299657599</v>
       </c>
       <c r="D44" t="n">
         <v>43</v>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S79</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.5399745325352203</v>
+        <v>0.6135511696864331</v>
       </c>
       <c r="D45" t="n">
         <v>44</v>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.5422080833277145</v>
+        <v>0.6183568982801889</v>
       </c>
       <c r="D46" t="n">
         <v>45</v>
@@ -1171,11 +1171,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.5424472754850664</v>
+        <v>0.6372310545687212</v>
       </c>
       <c r="D47" t="n">
         <v>46</v>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.5475103983506402</v>
+        <v>0.6387228815394025</v>
       </c>
       <c r="D48" t="n">
         <v>47</v>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.5503133858873539</v>
+        <v>0.675456641873503</v>
       </c>
       <c r="D49" t="n">
         <v>48</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>S28(5)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.5513697836534377</v>
+        <v>0.6879196415360052</v>
       </c>
       <c r="D50" t="n">
         <v>49</v>
@@ -1235,11 +1235,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.5561563520250102</v>
+        <v>0.7317719760849947</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.5576156513591051</v>
+        <v>0.7339863349705229</v>
       </c>
       <c r="D52" t="n">
         <v>51</v>
@@ -1267,11 +1267,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>019B</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.5579190477234698</v>
+        <v>0.7465135631616248</v>
       </c>
       <c r="D53" t="n">
         <v>52</v>
@@ -1283,11 +1283,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.5601275943142237</v>
+        <v>0.7690516142844713</v>
       </c>
       <c r="D54" t="n">
         <v>53</v>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>S58</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.5601444483024109</v>
+        <v>0.769345116326919</v>
       </c>
       <c r="D55" t="n">
         <v>54</v>
@@ -1315,11 +1315,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.5640676320858971</v>
+        <v>0.7910971372700197</v>
       </c>
       <c r="D56" t="n">
         <v>55</v>
@@ -1331,11 +1331,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>S102</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.5649295156080353</v>
+        <v>0.8414405896299196</v>
       </c>
       <c r="D57" t="n">
         <v>56</v>
@@ -1347,11 +1347,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.56806693376109</v>
+        <v>0.850042454471434</v>
       </c>
       <c r="D58" t="n">
         <v>57</v>
@@ -1363,11 +1363,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>S101</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.5710751553023293</v>
+        <v>0.8628174876049537</v>
       </c>
       <c r="D59" t="n">
         <v>58</v>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.5710865065096054</v>
+        <v>0.9029263946437102</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
@@ -1395,11 +1395,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.5722068049985606</v>
+        <v>0.9154427833611247</v>
       </c>
       <c r="D61" t="n">
         <v>60</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.5724960596840994</v>
+        <v>0.9159042099526967</v>
       </c>
       <c r="D62" t="n">
         <v>61</v>
@@ -1427,11 +1427,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.5744726564412542</v>
+        <v>0.9483297598528198</v>
       </c>
       <c r="D63" t="n">
         <v>62</v>
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.5772518883305402</v>
+        <v>0.9536585525384379</v>
       </c>
       <c r="D64" t="n">
         <v>63</v>
@@ -1459,11 +1459,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.5775632142418805</v>
+        <v>0.9648845432904982</v>
       </c>
       <c r="D65" t="n">
         <v>64</v>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.5803593991080923</v>
+        <v>0.9722756047535895</v>
       </c>
       <c r="D66" t="n">
         <v>65</v>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>S96</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.5804986749188547</v>
+        <v>0.986017827978479</v>
       </c>
       <c r="D67" t="n">
         <v>66</v>
@@ -1507,11 +1507,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.5814791967287359</v>
+        <v>0.9974300436367265</v>
       </c>
       <c r="D68" t="n">
         <v>67</v>
@@ -1523,11 +1523,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S67</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.5856717489409903</v>
+        <v>1.003131569158714</v>
       </c>
       <c r="D69" t="n">
         <v>68</v>
@@ -1539,11 +1539,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.5871527405550957</v>
+        <v>1.013142727929477</v>
       </c>
       <c r="D70" t="n">
         <v>69</v>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.5899256148787306</v>
+        <v>1.019001490209825</v>
       </c>
       <c r="D71" t="n">
         <v>70</v>
@@ -1571,11 +1571,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>S64</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.5926706541324308</v>
+        <v>1.025487315734785</v>
       </c>
       <c r="D72" t="n">
         <v>71</v>
@@ -1587,11 +1587,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>S95</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.5930481878495744</v>
+        <v>1.079572046917901</v>
       </c>
       <c r="D73" t="n">
         <v>72</v>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S21(5)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.5934093510114653</v>
+        <v>1.094157600689859</v>
       </c>
       <c r="D74" t="n">
         <v>73</v>
@@ -1619,11 +1619,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>042C</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.5966073432996783</v>
+        <v>1.096144918039989</v>
       </c>
       <c r="D75" t="n">
         <v>74</v>
@@ -1635,11 +1635,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>S63</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.6004826529035383</v>
+        <v>1.107286926342101</v>
       </c>
       <c r="D76" t="n">
         <v>75</v>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.600526352422122</v>
+        <v>1.114846676565727</v>
       </c>
       <c r="D77" t="n">
         <v>76</v>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.6009062358026265</v>
+        <v>1.133731828355369</v>
       </c>
       <c r="D78" t="n">
         <v>77</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.603074929859872</v>
+        <v>1.145913294481564</v>
       </c>
       <c r="D79" t="n">
         <v>78</v>
@@ -1699,11 +1699,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.6066125644216813</v>
+        <v>1.153587063923145</v>
       </c>
       <c r="D80" t="n">
         <v>79</v>
@@ -1715,11 +1715,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.6076986464554137</v>
+        <v>1.159301123999511</v>
       </c>
       <c r="D81" t="n">
         <v>80</v>
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.6084478435480961</v>
+        <v>1.159945263963395</v>
       </c>
       <c r="D82" t="n">
         <v>81</v>
@@ -1747,11 +1747,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>077B</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.6110652922305252</v>
+        <v>1.172734572661247</v>
       </c>
       <c r="D83" t="n">
         <v>82</v>
@@ -1763,11 +1763,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>104C</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.6129199325717485</v>
+        <v>1.177133058657776</v>
       </c>
       <c r="D84" t="n">
         <v>83</v>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>S99</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.6129973684613884</v>
+        <v>1.197834244546017</v>
       </c>
       <c r="D85" t="n">
         <v>84</v>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S40</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.6146018592525765</v>
+        <v>1.231274817110714</v>
       </c>
       <c r="D86" t="n">
         <v>85</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>072A</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.6154034604025812</v>
+        <v>1.236425197476465</v>
       </c>
       <c r="D87" t="n">
         <v>86</v>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.6168109707877535</v>
+        <v>1.238337014231035</v>
       </c>
       <c r="D88" t="n">
         <v>87</v>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.6176346785065769</v>
+        <v>1.25213874847473</v>
       </c>
       <c r="D89" t="n">
         <v>88</v>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.6178038292714395</v>
+        <v>1.257954690354242</v>
       </c>
       <c r="D90" t="n">
         <v>89</v>
@@ -1875,11 +1875,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>025B</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.6185465476509819</v>
+        <v>1.297408573733281</v>
       </c>
       <c r="D91" t="n">
         <v>90</v>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>057C</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.6200213455377179</v>
+        <v>1.337393455759457</v>
       </c>
       <c r="D92" t="n">
         <v>91</v>
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>098C</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.6213889412428641</v>
+        <v>1.375731789244887</v>
       </c>
       <c r="D93" t="n">
         <v>92</v>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>043ABC</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.62441601970585</v>
+        <v>1.390154119132507</v>
       </c>
       <c r="D94" t="n">
         <v>93</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.625912350805265</v>
+        <v>1.395703867641043</v>
       </c>
       <c r="D95" t="n">
         <v>94</v>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>030ABC</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.6261505446070396</v>
+        <v>1.396823502055015</v>
       </c>
       <c r="D96" t="n">
         <v>95</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>127B</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.6276808832828212</v>
+        <v>1.419031303557776</v>
       </c>
       <c r="D97" t="n">
         <v>96</v>
@@ -1987,11 +1987,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.6280847762652918</v>
+        <v>1.491828202025415</v>
       </c>
       <c r="D98" t="n">
         <v>97</v>
@@ -2003,11 +2003,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>143B</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.6300470945975647</v>
+        <v>1.494055001250989</v>
       </c>
       <c r="D99" t="n">
         <v>98</v>
@@ -2019,11 +2019,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>141B</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.6335293202176466</v>
+        <v>1.50832628214832</v>
       </c>
       <c r="D100" t="n">
         <v>99</v>
@@ -2035,11 +2035,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.6337650931900197</v>
+        <v>1.50995125235221</v>
       </c>
       <c r="D101" t="n">
         <v>100</v>
@@ -2051,11 +2051,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>117ABC</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.6354777360989823</v>
+        <v>1.580632863388202</v>
       </c>
       <c r="D102" t="n">
         <v>101</v>
@@ -2067,11 +2067,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S66</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.6365566232118295</v>
+        <v>1.60572455480436</v>
       </c>
       <c r="D103" t="n">
         <v>102</v>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S97</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.6373599866468866</v>
+        <v>1.625190742319843</v>
       </c>
       <c r="D104" t="n">
         <v>103</v>
@@ -2099,11 +2099,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.6374505489593454</v>
+        <v>1.631616508994628</v>
       </c>
       <c r="D105" t="n">
         <v>104</v>
@@ -2115,11 +2115,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>S78</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.6409648891583338</v>
+        <v>1.642200669253487</v>
       </c>
       <c r="D106" t="n">
         <v>105</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>145B</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.6414509573146536</v>
+        <v>1.65638967226272</v>
       </c>
       <c r="D107" t="n">
         <v>106</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>103A</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.6424842477783046</v>
+        <v>1.671309493066756</v>
       </c>
       <c r="D108" t="n">
         <v>107</v>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.6462142951592343</v>
+        <v>1.6943120196512</v>
       </c>
       <c r="D109" t="n">
         <v>108</v>
@@ -2179,11 +2179,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.646864932675818</v>
+        <v>1.701127217951179</v>
       </c>
       <c r="D110" t="n">
         <v>109</v>
@@ -2195,11 +2195,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.6469323701477642</v>
+        <v>1.712434519322673</v>
       </c>
       <c r="D111" t="n">
         <v>110</v>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>009B</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.6478839196008841</v>
+        <v>1.72542878264095</v>
       </c>
       <c r="D112" t="n">
         <v>111</v>
@@ -2227,11 +2227,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>024C</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.6503937151874452</v>
+        <v>1.750516170830915</v>
       </c>
       <c r="D113" t="n">
         <v>112</v>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>078B</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.6504124138009956</v>
+        <v>1.751073100130719</v>
       </c>
       <c r="D114" t="n">
         <v>113</v>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>066A</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.6512301012218443</v>
+        <v>1.755914530699477</v>
       </c>
       <c r="D115" t="n">
         <v>114</v>
@@ -2275,11 +2275,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>047ABC</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.6590007243578806</v>
+        <v>1.764210717020153</v>
       </c>
       <c r="D116" t="n">
         <v>115</v>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>016C</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.6705968300910684</v>
+        <v>1.782195423600141</v>
       </c>
       <c r="D117" t="n">
         <v>116</v>
@@ -2307,11 +2307,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>A53</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.6795732758109243</v>
+        <v>1.818686323504345</v>
       </c>
       <c r="D118" t="n">
         <v>117</v>
@@ -2323,11 +2323,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>149C</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.6822249116624723</v>
+        <v>1.828638938318954</v>
       </c>
       <c r="D119" t="n">
         <v>118</v>
@@ -2339,11 +2339,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>S80</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.6853216505185022</v>
+        <v>1.830723561361999</v>
       </c>
       <c r="D120" t="n">
         <v>119</v>
@@ -2355,11 +2355,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>014B</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.6899527436386715</v>
+        <v>1.872176383011477</v>
       </c>
       <c r="D121" t="n">
         <v>120</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>S46</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.6956384936740742</v>
+        <v>1.875976569729429</v>
       </c>
       <c r="D122" t="n">
         <v>121</v>
@@ -2387,11 +2387,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.6969720372659843</v>
+        <v>1.891855834533084</v>
       </c>
       <c r="D123" t="n">
         <v>122</v>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>148B</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.7001245106575487</v>
+        <v>1.909023305041172</v>
       </c>
       <c r="D124" t="n">
         <v>123</v>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>018A</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.7008729885720086</v>
+        <v>1.949847872202055</v>
       </c>
       <c r="D125" t="n">
         <v>124</v>
@@ -2435,11 +2435,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>137A</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.7037647680193277</v>
+        <v>1.977978767617577</v>
       </c>
       <c r="D126" t="n">
         <v>125</v>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>012A</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.7052528390632292</v>
+        <v>1.980082126228146</v>
       </c>
       <c r="D127" t="n">
         <v>126</v>
@@ -2467,11 +2467,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>S93</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.7065930542623292</v>
+        <v>1.998611902847312</v>
       </c>
       <c r="D128" t="n">
         <v>127</v>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>116B</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.7118508234353724</v>
+        <v>1.999527390187418</v>
       </c>
       <c r="D129" t="n">
         <v>128</v>
@@ -2499,11 +2499,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>023C</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.712579390219759</v>
+        <v>2.049351828762988</v>
       </c>
       <c r="D130" t="n">
         <v>129</v>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>115ABC</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.7155209006446386</v>
+        <v>2.07460541267196</v>
       </c>
       <c r="D131" t="n">
         <v>130</v>
@@ -2531,11 +2531,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>UCC1</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.7172240308022388</v>
+        <v>2.079321755205378</v>
       </c>
       <c r="D132" t="n">
         <v>131</v>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>102B</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.7177302982953639</v>
+        <v>2.082519693034055</v>
       </c>
       <c r="D133" t="n">
         <v>132</v>
@@ -2563,11 +2563,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>150B</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.7270061444809685</v>
+        <v>2.097144506609979</v>
       </c>
       <c r="D134" t="n">
         <v>133</v>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>132B</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.7300656900907722</v>
+        <v>2.098624495594011</v>
       </c>
       <c r="D135" t="n">
         <v>134</v>
@@ -2595,11 +2595,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>097ABC</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.7314660529615133</v>
+        <v>2.102291927982409</v>
       </c>
       <c r="D136" t="n">
         <v>135</v>
@@ -2611,11 +2611,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>136B</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.7317580553485201</v>
+        <v>2.111274559084756</v>
       </c>
       <c r="D137" t="n">
         <v>136</v>
@@ -2627,11 +2627,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>031A</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.7332544448199504</v>
+        <v>2.114576865878735</v>
       </c>
       <c r="D138" t="n">
         <v>137</v>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>022B</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.7357783871585788</v>
+        <v>2.14217953067516</v>
       </c>
       <c r="D139" t="n">
         <v>138</v>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>013A</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.7358294520311127</v>
+        <v>2.170404167423368</v>
       </c>
       <c r="D140" t="n">
         <v>139</v>
@@ -2675,11 +2675,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>092ABC</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.7374807311980002</v>
+        <v>2.190284421048478</v>
       </c>
       <c r="D141" t="n">
         <v>140</v>
@@ -2691,11 +2691,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>095A</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.7381203637182031</v>
+        <v>2.234811351149597</v>
       </c>
       <c r="D142" t="n">
         <v>141</v>
@@ -2707,11 +2707,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>021B</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.7403528954991712</v>
+        <v>2.240589840363225</v>
       </c>
       <c r="D143" t="n">
         <v>142</v>
@@ -2723,11 +2723,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.7419293129378134</v>
+        <v>2.256734289357667</v>
       </c>
       <c r="D144" t="n">
         <v>143</v>
@@ -2739,11 +2739,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>119B</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.7422970234339675</v>
+        <v>2.259100056813676</v>
       </c>
       <c r="D145" t="n">
         <v>144</v>
@@ -2755,11 +2755,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>085C</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.7451698833102089</v>
+        <v>2.259695112876489</v>
       </c>
       <c r="D146" t="n">
         <v>145</v>
@@ -2771,11 +2771,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>128B</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.7478199928277829</v>
+        <v>2.261944630732623</v>
       </c>
       <c r="D147" t="n">
         <v>146</v>
@@ -2787,11 +2787,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>146B</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.7518632452480585</v>
+        <v>2.266442758183566</v>
       </c>
       <c r="D148" t="n">
         <v>147</v>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>005ABC</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.7549672201377287</v>
+        <v>2.27731399542493</v>
       </c>
       <c r="D149" t="n">
         <v>148</v>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.7553621744720782</v>
+        <v>2.297080782692796</v>
       </c>
       <c r="D150" t="n">
         <v>149</v>
@@ -2835,11 +2835,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>S83</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.7637891954072916</v>
+        <v>2.310418664325629</v>
       </c>
       <c r="D151" t="n">
         <v>150</v>
@@ -2851,11 +2851,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>044A</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.7651163916690356</v>
+        <v>2.329091938623054</v>
       </c>
       <c r="D152" t="n">
         <v>151</v>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>017B</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.7659301314080673</v>
+        <v>2.331876477399435</v>
       </c>
       <c r="D153" t="n">
         <v>152</v>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>144B</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.7667095077809323</v>
+        <v>2.342495426879799</v>
       </c>
       <c r="D154" t="n">
         <v>153</v>
@@ -2899,11 +2899,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>S100</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.7693003371589151</v>
+        <v>2.345119257307775</v>
       </c>
       <c r="D155" t="n">
         <v>154</v>
@@ -2915,11 +2915,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>065C</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.7704970058097398</v>
+        <v>2.354622465982963</v>
       </c>
       <c r="D156" t="n">
         <v>155</v>
@@ -2931,11 +2931,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>S87</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>0.77131020120551</v>
+        <v>2.374797188301778</v>
       </c>
       <c r="D157" t="n">
         <v>156</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>142C</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0.7887574063130198</v>
+        <v>2.386608600933051</v>
       </c>
       <c r="D158" t="n">
         <v>157</v>
@@ -2963,11 +2963,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.7891204243184647</v>
+        <v>2.404075708339076</v>
       </c>
       <c r="D159" t="n">
         <v>158</v>
@@ -2979,11 +2979,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>DBC2</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0.791652672702895</v>
+        <v>2.426258453264439</v>
       </c>
       <c r="D160" t="n">
         <v>159</v>
@@ -2995,11 +2995,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>129A</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.7918350375648093</v>
+        <v>2.447053049583766</v>
       </c>
       <c r="D161" t="n">
         <v>160</v>
@@ -3011,11 +3011,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>134C</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0.7927824614648837</v>
+        <v>2.462421000713577</v>
       </c>
       <c r="D162" t="n">
         <v>161</v>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>UCE1</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.7953765230546896</v>
+        <v>2.479427488290719</v>
       </c>
       <c r="D163" t="n">
         <v>162</v>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>118A</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.7968850694695153</v>
+        <v>2.490543804887305</v>
       </c>
       <c r="D164" t="n">
         <v>163</v>
@@ -3059,11 +3059,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>114B</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.7973251537487782</v>
+        <v>2.496300783960359</v>
       </c>
       <c r="D165" t="n">
         <v>164</v>
@@ -3075,11 +3075,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>083B</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.7992003819160949</v>
+        <v>2.519851425934307</v>
       </c>
       <c r="D166" t="n">
         <v>165</v>
@@ -3091,11 +3091,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.8010756606369889</v>
+        <v>2.533528760030684</v>
       </c>
       <c r="D167" t="n">
         <v>166</v>
@@ -3107,11 +3107,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>MCE2</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.8016283830315825</v>
+        <v>2.572324085095787</v>
       </c>
       <c r="D168" t="n">
         <v>167</v>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>048C</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.8068000919688815</v>
+        <v>2.640973257360858</v>
       </c>
       <c r="D169" t="n">
         <v>168</v>
@@ -3139,11 +3139,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.8082516259482172</v>
+        <v>2.644770402642359</v>
       </c>
       <c r="D170" t="n">
         <v>169</v>
@@ -3155,11 +3155,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>008A</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.8095796148110737</v>
+        <v>2.689290658553455</v>
       </c>
       <c r="D171" t="n">
         <v>170</v>
@@ -3171,11 +3171,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>093C</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0.8117628853166764</v>
+        <v>2.74901437268143</v>
       </c>
       <c r="D172" t="n">
         <v>171</v>
@@ -3187,11 +3187,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>027B</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0.8123680146659075</v>
+        <v>2.760509079714799</v>
       </c>
       <c r="D173" t="n">
         <v>172</v>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>003ABC</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.8162924654769743</v>
+        <v>2.763479807123514</v>
       </c>
       <c r="D174" t="n">
         <v>173</v>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>A58</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.8170967647078101</v>
+        <v>2.828166794916441</v>
       </c>
       <c r="D175" t="n">
         <v>174</v>
@@ -3235,11 +3235,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>067B</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.819192150054835</v>
+        <v>2.831748300360889</v>
       </c>
       <c r="D176" t="n">
         <v>175</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>UBC1</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>0.8219680459459473</v>
+        <v>2.84582826505566</v>
       </c>
       <c r="D177" t="n">
         <v>176</v>
@@ -3267,11 +3267,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>090B</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>0.8229620343245406</v>
+        <v>2.867646459747699</v>
       </c>
       <c r="D178" t="n">
         <v>177</v>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>029C</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.8253991727079085</v>
+        <v>2.890769349844495</v>
       </c>
       <c r="D179" t="n">
         <v>178</v>
@@ -3299,11 +3299,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.8256982409959298</v>
+        <v>2.89246897692229</v>
       </c>
       <c r="D180" t="n">
         <v>179</v>
@@ -3315,11 +3315,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>059ABC</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.830568356786174</v>
+        <v>2.917489125100054</v>
       </c>
       <c r="D181" t="n">
         <v>180</v>
@@ -3331,11 +3331,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>106B</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0.8330840616624919</v>
+        <v>2.924915352577265</v>
       </c>
       <c r="D182" t="n">
         <v>181</v>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>S98</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.834081369310496</v>
+        <v>2.951036662966345</v>
       </c>
       <c r="D183" t="n">
         <v>182</v>
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>082A</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.836022752643399</v>
+        <v>2.96181698670493</v>
       </c>
       <c r="D184" t="n">
         <v>183</v>
@@ -3379,11 +3379,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>131B</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.8371829803608046</v>
+        <v>2.963231493334849</v>
       </c>
       <c r="D185" t="n">
         <v>184</v>
@@ -3395,11 +3395,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>130A</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.8377669859084637</v>
+        <v>2.980226863603674</v>
       </c>
       <c r="D186" t="n">
         <v>185</v>
@@ -3411,11 +3411,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>034C</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0.8402115464951354</v>
+        <v>2.981908648169002</v>
       </c>
       <c r="D187" t="n">
         <v>186</v>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>100C</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0.8404195797588516</v>
+        <v>2.993905594326431</v>
       </c>
       <c r="D188" t="n">
         <v>187</v>
@@ -3443,11 +3443,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>037B</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.8462082812769164</v>
+        <v>3.008968663813961</v>
       </c>
       <c r="D189" t="n">
         <v>188</v>
@@ -3459,11 +3459,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>070B</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0.8479939113629964</v>
+        <v>3.029942607617384</v>
       </c>
       <c r="D190" t="n">
         <v>189</v>
@@ -3475,11 +3475,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>105C</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.8493559187984098</v>
+        <v>3.102842087588441</v>
       </c>
       <c r="D191" t="n">
         <v>190</v>
@@ -3491,11 +3491,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>S27(5)</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.8498365014758507</v>
+        <v>3.144907615587742</v>
       </c>
       <c r="D192" t="n">
         <v>191</v>
@@ -3507,11 +3507,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>091C</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.8684307388725729</v>
+        <v>3.201937143472751</v>
       </c>
       <c r="D193" t="n">
         <v>192</v>
@@ -3523,11 +3523,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>126A</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.8693874790905177</v>
+        <v>3.216623186227426</v>
       </c>
       <c r="D194" t="n">
         <v>193</v>
@@ -3539,11 +3539,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>S89</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.8696275423735416</v>
+        <v>3.221471462810959</v>
       </c>
       <c r="D195" t="n">
         <v>194</v>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>135A</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0.8697147900844762</v>
+        <v>3.302504865988261</v>
       </c>
       <c r="D196" t="n">
         <v>195</v>
@@ -3571,11 +3571,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>S94</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.8719927416615398</v>
+        <v>3.308387244945979</v>
       </c>
       <c r="D197" t="n">
         <v>196</v>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>0.8723671399685544</v>
+        <v>3.342005881826272</v>
       </c>
       <c r="D198" t="n">
         <v>197</v>
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>107C</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>0.8776809367945191</v>
+        <v>3.362997082671668</v>
       </c>
       <c r="D199" t="n">
         <v>198</v>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>S84</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.8810332524590305</v>
+        <v>3.388877017626667</v>
       </c>
       <c r="D200" t="n">
         <v>199</v>
@@ -3635,11 +3635,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>UJC1</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.8822790391143867</v>
+        <v>3.406731806065343</v>
       </c>
       <c r="D201" t="n">
         <v>200</v>
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>113B</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.889267526655467</v>
+        <v>3.419836466439655</v>
       </c>
       <c r="D202" t="n">
         <v>201</v>
@@ -3667,11 +3667,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>086A</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0.903183418158147</v>
+        <v>3.441225940226508</v>
       </c>
       <c r="D203" t="n">
         <v>202</v>
@@ -3683,11 +3683,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>DJC2</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>0.9034678722125055</v>
+        <v>3.471640522215216</v>
       </c>
       <c r="D204" t="n">
         <v>203</v>
@@ -3699,11 +3699,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>045B</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.9115225033341499</v>
+        <v>3.496490641299062</v>
       </c>
       <c r="D205" t="n">
         <v>204</v>
@@ -3715,11 +3715,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>DCE3</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.9165246489772899</v>
+        <v>3.513996231819244</v>
       </c>
       <c r="D206" t="n">
         <v>205</v>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>123A</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.9215996131933117</v>
+        <v>3.55318567121627</v>
       </c>
       <c r="D207" t="n">
         <v>206</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>054B</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.923814068391583</v>
+        <v>3.557871964241698</v>
       </c>
       <c r="D208" t="n">
         <v>207</v>
@@ -3763,11 +3763,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>124A</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.9243267853069075</v>
+        <v>3.628259546920428</v>
       </c>
       <c r="D209" t="n">
         <v>208</v>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>099C</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.9272890782070158</v>
+        <v>3.650971145561097</v>
       </c>
       <c r="D210" t="n">
         <v>209</v>
@@ -3795,11 +3795,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>015C</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.9334990011324412</v>
+        <v>3.660881940237104</v>
       </c>
       <c r="D211" t="n">
         <v>210</v>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>096A</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.9395089289547327</v>
+        <v>3.67803512406718</v>
       </c>
       <c r="D212" t="n">
         <v>211</v>
@@ -3827,11 +3827,11 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>055C</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.9423048753384816</v>
+        <v>3.681838434817529</v>
       </c>
       <c r="D213" t="n">
         <v>212</v>
@@ -3843,11 +3843,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.9444986096343727</v>
+        <v>3.738640352011697</v>
       </c>
       <c r="D214" t="n">
         <v>213</v>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>049A</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0.9502781173816847</v>
+        <v>3.831779336136942</v>
       </c>
       <c r="D215" t="n">
         <v>214</v>
@@ -3875,11 +3875,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>069A</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0.9508253203478138</v>
+        <v>3.859064533468148</v>
       </c>
       <c r="D216" t="n">
         <v>215</v>
@@ -3891,11 +3891,11 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>084A</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>0.9521524407998946</v>
+        <v>3.882269467735987</v>
       </c>
       <c r="D217" t="n">
         <v>216</v>
@@ -3907,11 +3907,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>080C</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.9521888956593905</v>
+        <v>3.927630929673222</v>
       </c>
       <c r="D218" t="n">
         <v>217</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.9533573171392666</v>
+        <v>3.975472939029722</v>
       </c>
       <c r="D219" t="n">
         <v>218</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.9557272924072273</v>
+        <v>4.113098870499632</v>
       </c>
       <c r="D220" t="n">
         <v>219</v>
@@ -3955,11 +3955,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>140C</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.9558323625751309</v>
+        <v>4.234344600914814</v>
       </c>
       <c r="D221" t="n">
         <v>220</v>
@@ -3971,11 +3971,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>074B</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0.9585577371642899</v>
+        <v>4.253570297804814</v>
       </c>
       <c r="D222" t="n">
         <v>221</v>
@@ -3987,11 +3987,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>075A</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.9597483543529494</v>
+        <v>4.292117288815221</v>
       </c>
       <c r="D223" t="n">
         <v>222</v>
@@ -4003,11 +4003,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>108B</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0.9647952907770359</v>
+        <v>4.314021542726616</v>
       </c>
       <c r="D224" t="n">
         <v>223</v>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>081B</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0.9684163502568556</v>
+        <v>4.391681541309022</v>
       </c>
       <c r="D225" t="n">
         <v>224</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>S85</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0.9692453361367768</v>
+        <v>4.468968995683205</v>
       </c>
       <c r="D226" t="n">
         <v>225</v>
@@ -4051,11 +4051,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>138B</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0.9775067813330917</v>
+        <v>4.537863287148288</v>
       </c>
       <c r="D227" t="n">
         <v>226</v>
@@ -4067,11 +4067,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>089A</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>0.9779984231567342</v>
+        <v>4.641127841209785</v>
       </c>
       <c r="D228" t="n">
         <v>227</v>
@@ -4083,11 +4083,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>079C</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>0.9905182490356108</v>
+        <v>5.165385367077522</v>
       </c>
       <c r="D229" t="n">
         <v>228</v>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>088C</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>5.600905185773277</v>
       </c>
       <c r="D230" t="n">
         <v>229</v>
@@ -4115,11 +4115,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>101C</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>5.994649004624828</v>
       </c>
       <c r="D231" t="n">
         <v>230</v>
@@ -4131,11 +4131,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>052B</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>6.555506950144018</v>
       </c>
       <c r="D232" t="n">
         <v>231</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>076ABC</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>6.721331834074801</v>
       </c>
       <c r="D233" t="n">
         <v>232</v>
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>147A</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>6.842172179612913</v>
       </c>
       <c r="D234" t="n">
         <v>233</v>

--- a/results/01_pollution_assessment/PCA_Stressors/tables/MaxRel_site_rankings.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/MaxRel_site_rankings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D234"/>
+  <dimension ref="A1:D311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,11 +451,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.4022551669291249</v>
+        <v>0.3462664435142515</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -467,11 +467,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.2280902140263398</v>
+        <v>0.3496776445458151</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.1685092747940378</v>
+        <v>0.3797930998848826</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -499,11 +499,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.1262227552824805</v>
+        <v>0.3953345663194837</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -515,11 +515,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01017673150811147</v>
+        <v>0.4274371806522259</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -531,11 +531,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02075406377236158</v>
+        <v>0.4297337860557036</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -547,11 +547,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02202355758647872</v>
+        <v>0.4323533622575924</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -563,11 +563,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03006659771482753</v>
+        <v>0.4444414212074977</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -579,11 +579,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.05587728398447637</v>
+        <v>0.4464897872875588</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -595,11 +595,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.05674552872975166</v>
+        <v>0.4576832611049282</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -611,11 +611,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1831052725646437</v>
+        <v>0.458149766195094</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -627,11 +627,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1906505373581875</v>
+        <v>0.4692844653483959</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -643,11 +643,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2080320203356396</v>
+        <v>0.4708173402063078</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
@@ -659,11 +659,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2316925153583238</v>
+        <v>0.4715512418627715</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2442386661857714</v>
+        <v>0.4729255558296746</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -691,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2549825368686213</v>
+        <v>0.4775085652735411</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -707,11 +707,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.2620814423873599</v>
+        <v>0.4787220558854894</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -723,11 +723,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.28106403645769</v>
+        <v>0.4816654691901178</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -739,11 +739,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2843845156874721</v>
+        <v>0.4900975712348741</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -755,11 +755,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.2864756987871691</v>
+        <v>0.5022633860461179</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
@@ -771,11 +771,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.2947578242478518</v>
+        <v>0.5045175164105158</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
@@ -787,11 +787,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.3002658069252208</v>
+        <v>0.509303522998426</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
@@ -803,11 +803,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3010141847338035</v>
+        <v>0.5144833254877228</v>
       </c>
       <c r="D24" t="n">
         <v>23</v>
@@ -819,11 +819,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3017315555677913</v>
+        <v>0.5150666365022126</v>
       </c>
       <c r="D25" t="n">
         <v>24</v>
@@ -835,11 +835,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3020051722514078</v>
+        <v>0.5153620397658929</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
@@ -851,11 +851,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.3135571086324083</v>
+        <v>0.5179081261241051</v>
       </c>
       <c r="D27" t="n">
         <v>26</v>
@@ -867,11 +867,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.3289455898705217</v>
+        <v>0.5211362625251322</v>
       </c>
       <c r="D28" t="n">
         <v>27</v>
@@ -883,11 +883,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.3316121209436056</v>
+        <v>0.5242655307301869</v>
       </c>
       <c r="D29" t="n">
         <v>28</v>
@@ -899,11 +899,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.3327282763969321</v>
+        <v>0.535477548742438</v>
       </c>
       <c r="D30" t="n">
         <v>29</v>
@@ -915,11 +915,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.3357388722078157</v>
+        <v>0.5373798236202265</v>
       </c>
       <c r="D31" t="n">
         <v>30</v>
@@ -931,11 +931,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.3593948198147103</v>
+        <v>0.5401328628551662</v>
       </c>
       <c r="D32" t="n">
         <v>31</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.3859934558355891</v>
+        <v>0.5403383870452557</v>
       </c>
       <c r="D33" t="n">
         <v>32</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.3952472834481091</v>
+        <v>0.5405769473162717</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
@@ -979,11 +979,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.4202137105699785</v>
+        <v>0.5429295692833933</v>
       </c>
       <c r="D35" t="n">
         <v>34</v>
@@ -995,11 +995,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.4203976788765076</v>
+        <v>0.543273883175983</v>
       </c>
       <c r="D36" t="n">
         <v>35</v>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.4546077021090476</v>
+        <v>0.5446988021022459</v>
       </c>
       <c r="D37" t="n">
         <v>36</v>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.4712671734293135</v>
+        <v>0.5486565835616674</v>
       </c>
       <c r="D38" t="n">
         <v>37</v>
@@ -1043,11 +1043,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.4825169087612939</v>
+        <v>0.5557877595112918</v>
       </c>
       <c r="D39" t="n">
         <v>38</v>
@@ -1059,11 +1059,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.5202305328356266</v>
+        <v>0.5603453196095525</v>
       </c>
       <c r="D40" t="n">
         <v>39</v>
@@ -1075,11 +1075,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.5325111195530996</v>
+        <v>0.5676893132633262</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.5522479520124634</v>
+        <v>0.5699832652486376</v>
       </c>
       <c r="D42" t="n">
         <v>41</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.5942638348690173</v>
+        <v>0.572305892231565</v>
       </c>
       <c r="D43" t="n">
         <v>42</v>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.599459299657599</v>
+        <v>0.5744284821124763</v>
       </c>
       <c r="D44" t="n">
         <v>43</v>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.6135511696864331</v>
+        <v>0.5786790716722673</v>
       </c>
       <c r="D45" t="n">
         <v>44</v>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.6183568982801889</v>
+        <v>0.5864290829592963</v>
       </c>
       <c r="D46" t="n">
         <v>45</v>
@@ -1171,11 +1171,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.6372310545687212</v>
+        <v>0.586468408188435</v>
       </c>
       <c r="D47" t="n">
         <v>46</v>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.6387228815394025</v>
+        <v>0.5977184367277821</v>
       </c>
       <c r="D48" t="n">
         <v>47</v>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.675456641873503</v>
+        <v>0.5980999040592121</v>
       </c>
       <c r="D49" t="n">
         <v>48</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.6879196415360052</v>
+        <v>0.599367293516583</v>
       </c>
       <c r="D50" t="n">
         <v>49</v>
@@ -1235,11 +1235,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>DR-148</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.7317719760849947</v>
+        <v>0.6001254785412375</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.7339863349705229</v>
+        <v>0.6061398275077845</v>
       </c>
       <c r="D52" t="n">
         <v>51</v>
@@ -1267,11 +1267,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.7465135631616248</v>
+        <v>0.6076758252386268</v>
       </c>
       <c r="D53" t="n">
         <v>52</v>
@@ -1283,11 +1283,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.7690516142844713</v>
+        <v>0.6136105454847579</v>
       </c>
       <c r="D54" t="n">
         <v>53</v>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.769345116326919</v>
+        <v>0.6151889609011129</v>
       </c>
       <c r="D55" t="n">
         <v>54</v>
@@ -1315,11 +1315,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.7910971372700197</v>
+        <v>0.6177431158635652</v>
       </c>
       <c r="D56" t="n">
         <v>55</v>
@@ -1331,11 +1331,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.8414405896299196</v>
+        <v>0.6224788783341002</v>
       </c>
       <c r="D57" t="n">
         <v>56</v>
@@ -1347,11 +1347,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.850042454471434</v>
+        <v>0.6235231547056608</v>
       </c>
       <c r="D58" t="n">
         <v>57</v>
@@ -1363,11 +1363,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.8628174876049537</v>
+        <v>0.6236700881102278</v>
       </c>
       <c r="D59" t="n">
         <v>58</v>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.9029263946437102</v>
+        <v>0.62521936092718</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
@@ -1395,11 +1395,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.9154427833611247</v>
+        <v>0.6264430050939052</v>
       </c>
       <c r="D61" t="n">
         <v>60</v>
@@ -1411,11 +1411,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.9159042099526967</v>
+        <v>0.6320240906632355</v>
       </c>
       <c r="D62" t="n">
         <v>61</v>
@@ -1427,11 +1427,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.9483297598528198</v>
+        <v>0.6330377273190512</v>
       </c>
       <c r="D63" t="n">
         <v>62</v>
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.9536585525384379</v>
+        <v>0.6335103192287275</v>
       </c>
       <c r="D64" t="n">
         <v>63</v>
@@ -1459,11 +1459,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.9648845432904982</v>
+        <v>0.6372522329272635</v>
       </c>
       <c r="D65" t="n">
         <v>64</v>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.9722756047535895</v>
+        <v>0.6375697175070046</v>
       </c>
       <c r="D66" t="n">
         <v>65</v>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.986017827978479</v>
+        <v>0.6379846389462813</v>
       </c>
       <c r="D67" t="n">
         <v>66</v>
@@ -1507,11 +1507,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>LSC-36</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.9974300436367265</v>
+        <v>0.6385451469597292</v>
       </c>
       <c r="D68" t="n">
         <v>67</v>
@@ -1523,11 +1523,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.003131569158714</v>
+        <v>0.63962072753053</v>
       </c>
       <c r="D69" t="n">
         <v>68</v>
@@ -1539,11 +1539,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.013142727929477</v>
+        <v>0.6463420735679341</v>
       </c>
       <c r="D70" t="n">
         <v>69</v>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.019001490209825</v>
+        <v>0.6493889968254914</v>
       </c>
       <c r="D71" t="n">
         <v>70</v>
@@ -1571,11 +1571,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.025487315734785</v>
+        <v>0.649827934219272</v>
       </c>
       <c r="D72" t="n">
         <v>71</v>
@@ -1587,11 +1587,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.079572046917901</v>
+        <v>0.6568404026702845</v>
       </c>
       <c r="D73" t="n">
         <v>72</v>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.094157600689859</v>
+        <v>0.6572643504002024</v>
       </c>
       <c r="D74" t="n">
         <v>73</v>
@@ -1619,11 +1619,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.096144918039989</v>
+        <v>0.6584238892571777</v>
       </c>
       <c r="D75" t="n">
         <v>74</v>
@@ -1635,11 +1635,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>DR-150</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.107286926342101</v>
+        <v>0.6596319478791576</v>
       </c>
       <c r="D76" t="n">
         <v>75</v>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.114846676565727</v>
+        <v>0.6610357787448649</v>
       </c>
       <c r="D77" t="n">
         <v>76</v>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>LSC-28</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.133731828355369</v>
+        <v>0.6628233064264522</v>
       </c>
       <c r="D78" t="n">
         <v>77</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.145913294481564</v>
+        <v>0.6634947298958765</v>
       </c>
       <c r="D79" t="n">
         <v>78</v>
@@ -1699,11 +1699,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.153587063923145</v>
+        <v>0.6642859200112887</v>
       </c>
       <c r="D80" t="n">
         <v>79</v>
@@ -1715,11 +1715,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.159301123999511</v>
+        <v>0.6652982584732056</v>
       </c>
       <c r="D81" t="n">
         <v>80</v>
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.159945263963395</v>
+        <v>0.6670386647178785</v>
       </c>
       <c r="D82" t="n">
         <v>81</v>
@@ -1747,11 +1747,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>LSC-65</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.172734572661247</v>
+        <v>0.6714622266199197</v>
       </c>
       <c r="D83" t="n">
         <v>82</v>
@@ -1763,11 +1763,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.177133058657776</v>
+        <v>0.6727244975258698</v>
       </c>
       <c r="D84" t="n">
         <v>83</v>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.197834244546017</v>
+        <v>0.6735729211664</v>
       </c>
       <c r="D85" t="n">
         <v>84</v>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.231274817110714</v>
+        <v>0.6759971933216478</v>
       </c>
       <c r="D86" t="n">
         <v>85</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.236425197476465</v>
+        <v>0.6767709009360195</v>
       </c>
       <c r="D87" t="n">
         <v>86</v>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.238337014231035</v>
+        <v>0.677158075652446</v>
       </c>
       <c r="D88" t="n">
         <v>87</v>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.25213874847473</v>
+        <v>0.6781982309307213</v>
       </c>
       <c r="D89" t="n">
         <v>88</v>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.257954690354242</v>
+        <v>0.6786659525735743</v>
       </c>
       <c r="D90" t="n">
         <v>89</v>
@@ -1875,11 +1875,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.297408573733281</v>
+        <v>0.6787130942897357</v>
       </c>
       <c r="D91" t="n">
         <v>90</v>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.337393455759457</v>
+        <v>0.6794235773022457</v>
       </c>
       <c r="D92" t="n">
         <v>91</v>
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.375731789244887</v>
+        <v>0.6816214642310559</v>
       </c>
       <c r="D93" t="n">
         <v>92</v>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>DR-155</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.390154119132507</v>
+        <v>0.6820658159350247</v>
       </c>
       <c r="D94" t="n">
         <v>93</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.395703867641043</v>
+        <v>0.6825596691810616</v>
       </c>
       <c r="D95" t="n">
         <v>94</v>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.396823502055015</v>
+        <v>0.6839651506591352</v>
       </c>
       <c r="D96" t="n">
         <v>95</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.419031303557776</v>
+        <v>0.6862662803391393</v>
       </c>
       <c r="D97" t="n">
         <v>96</v>
@@ -1987,11 +1987,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.491828202025415</v>
+        <v>0.6871039479750344</v>
       </c>
       <c r="D98" t="n">
         <v>97</v>
@@ -2003,11 +2003,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>LSC-52</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.494055001250989</v>
+        <v>0.6879323295104336</v>
       </c>
       <c r="D99" t="n">
         <v>98</v>
@@ -2019,11 +2019,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.50832628214832</v>
+        <v>0.6883530825580165</v>
       </c>
       <c r="D100" t="n">
         <v>99</v>
@@ -2035,11 +2035,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>LSC-46</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.50995125235221</v>
+        <v>0.688946470309342</v>
       </c>
       <c r="D101" t="n">
         <v>100</v>
@@ -2051,11 +2051,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.580632863388202</v>
+        <v>0.6891259922174557</v>
       </c>
       <c r="D102" t="n">
         <v>101</v>
@@ -2067,11 +2067,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1.60572455480436</v>
+        <v>0.6901307836523848</v>
       </c>
       <c r="D103" t="n">
         <v>102</v>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.625190742319843</v>
+        <v>0.6907225076894121</v>
       </c>
       <c r="D104" t="n">
         <v>103</v>
@@ -2099,11 +2099,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1.631616508994628</v>
+        <v>0.6910592667626752</v>
       </c>
       <c r="D105" t="n">
         <v>104</v>
@@ -2115,11 +2115,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1.642200669253487</v>
+        <v>0.6912858326251796</v>
       </c>
       <c r="D106" t="n">
         <v>105</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.65638967226272</v>
+        <v>0.6921248468989928</v>
       </c>
       <c r="D107" t="n">
         <v>106</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1.671309493066756</v>
+        <v>0.6929886330659415</v>
       </c>
       <c r="D108" t="n">
         <v>107</v>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.6943120196512</v>
+        <v>0.6941403720124526</v>
       </c>
       <c r="D109" t="n">
         <v>108</v>
@@ -2179,11 +2179,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1.701127217951179</v>
+        <v>0.6944317164075668</v>
       </c>
       <c r="D110" t="n">
         <v>109</v>
@@ -2195,11 +2195,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1.712434519322673</v>
+        <v>0.6951348967947746</v>
       </c>
       <c r="D111" t="n">
         <v>110</v>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.72542878264095</v>
+        <v>0.6953165687219887</v>
       </c>
       <c r="D112" t="n">
         <v>111</v>
@@ -2227,11 +2227,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1.750516170830915</v>
+        <v>0.6967083716077178</v>
       </c>
       <c r="D113" t="n">
         <v>112</v>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1.751073100130719</v>
+        <v>0.6968749626024541</v>
       </c>
       <c r="D114" t="n">
         <v>113</v>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.755914530699477</v>
+        <v>0.6970599698633732</v>
       </c>
       <c r="D115" t="n">
         <v>114</v>
@@ -2275,11 +2275,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1.764210717020153</v>
+        <v>0.6975876019022981</v>
       </c>
       <c r="D116" t="n">
         <v>115</v>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1.782195423600141</v>
+        <v>0.6988239736851856</v>
       </c>
       <c r="D117" t="n">
         <v>116</v>
@@ -2307,11 +2307,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1.818686323504345</v>
+        <v>0.6989828294221436</v>
       </c>
       <c r="D118" t="n">
         <v>117</v>
@@ -2323,11 +2323,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.828638938318954</v>
+        <v>0.6998952330351882</v>
       </c>
       <c r="D119" t="n">
         <v>118</v>
@@ -2339,11 +2339,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1.830723561361999</v>
+        <v>0.7001862130550459</v>
       </c>
       <c r="D120" t="n">
         <v>119</v>
@@ -2355,11 +2355,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>LSC-51</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.872176383011477</v>
+        <v>0.7002583724763561</v>
       </c>
       <c r="D121" t="n">
         <v>120</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1.875976569729429</v>
+        <v>0.7010789395130795</v>
       </c>
       <c r="D122" t="n">
         <v>121</v>
@@ -2387,11 +2387,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1.891855834533084</v>
+        <v>0.701591073475354</v>
       </c>
       <c r="D123" t="n">
         <v>122</v>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.909023305041172</v>
+        <v>0.7027791599877119</v>
       </c>
       <c r="D124" t="n">
         <v>123</v>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1.949847872202055</v>
+        <v>0.7049071112370577</v>
       </c>
       <c r="D125" t="n">
         <v>124</v>
@@ -2435,11 +2435,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1.977978767617577</v>
+        <v>0.7051247739663712</v>
       </c>
       <c r="D126" t="n">
         <v>125</v>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1.980082126228146</v>
+        <v>0.7067385526341784</v>
       </c>
       <c r="D127" t="n">
         <v>126</v>
@@ -2467,11 +2467,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>DR-152</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1.998611902847312</v>
+        <v>0.7073827715297302</v>
       </c>
       <c r="D128" t="n">
         <v>127</v>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.999527390187418</v>
+        <v>0.708180528446253</v>
       </c>
       <c r="D129" t="n">
         <v>128</v>
@@ -2499,11 +2499,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2.049351828762988</v>
+        <v>0.7089357009530139</v>
       </c>
       <c r="D130" t="n">
         <v>129</v>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2.07460541267196</v>
+        <v>0.7129910633674774</v>
       </c>
       <c r="D131" t="n">
         <v>130</v>
@@ -2531,11 +2531,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2.079321755205378</v>
+        <v>0.7131379826387567</v>
       </c>
       <c r="D132" t="n">
         <v>131</v>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2.082519693034055</v>
+        <v>0.7141098707611813</v>
       </c>
       <c r="D133" t="n">
         <v>132</v>
@@ -2563,11 +2563,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2.097144506609979</v>
+        <v>0.7144824215235126</v>
       </c>
       <c r="D134" t="n">
         <v>133</v>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2.098624495594011</v>
+        <v>0.7145910395821197</v>
       </c>
       <c r="D135" t="n">
         <v>134</v>
@@ -2595,11 +2595,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2.102291927982409</v>
+        <v>0.7158177983131931</v>
       </c>
       <c r="D136" t="n">
         <v>135</v>
@@ -2611,11 +2611,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>LSC-61</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2.111274559084756</v>
+        <v>0.7158750936210641</v>
       </c>
       <c r="D137" t="n">
         <v>136</v>
@@ -2627,11 +2627,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2.114576865878735</v>
+        <v>0.7169758132890097</v>
       </c>
       <c r="D138" t="n">
         <v>137</v>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2.14217953067516</v>
+        <v>0.7170522186918294</v>
       </c>
       <c r="D139" t="n">
         <v>138</v>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2.170404167423368</v>
+        <v>0.7171367419651229</v>
       </c>
       <c r="D140" t="n">
         <v>139</v>
@@ -2675,11 +2675,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>LSC-29</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2.190284421048478</v>
+        <v>0.7178469187412199</v>
       </c>
       <c r="D141" t="n">
         <v>140</v>
@@ -2691,11 +2691,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2.234811351149597</v>
+        <v>0.7185018930126073</v>
       </c>
       <c r="D142" t="n">
         <v>141</v>
@@ -2707,11 +2707,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>LSC-54</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2.240589840363225</v>
+        <v>0.7190915119023116</v>
       </c>
       <c r="D143" t="n">
         <v>142</v>
@@ -2723,11 +2723,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2.256734289357667</v>
+        <v>0.7210604300280651</v>
       </c>
       <c r="D144" t="n">
         <v>143</v>
@@ -2739,11 +2739,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>DR-156</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2.259100056813676</v>
+        <v>0.722596144817865</v>
       </c>
       <c r="D145" t="n">
         <v>144</v>
@@ -2755,11 +2755,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2.259695112876489</v>
+        <v>0.7231663103585916</v>
       </c>
       <c r="D146" t="n">
         <v>145</v>
@@ -2771,11 +2771,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2.261944630732623</v>
+        <v>0.7239428412631888</v>
       </c>
       <c r="D147" t="n">
         <v>146</v>
@@ -2787,11 +2787,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>LSC-66</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2.266442758183566</v>
+        <v>0.7245351284672582</v>
       </c>
       <c r="D148" t="n">
         <v>147</v>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2.27731399542493</v>
+        <v>0.7252582526111437</v>
       </c>
       <c r="D149" t="n">
         <v>148</v>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2.297080782692796</v>
+        <v>0.7259281554620718</v>
       </c>
       <c r="D150" t="n">
         <v>149</v>
@@ -2835,11 +2835,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2.310418664325629</v>
+        <v>0.7262596168259837</v>
       </c>
       <c r="D151" t="n">
         <v>150</v>
@@ -2851,11 +2851,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2.329091938623054</v>
+        <v>0.726732807445975</v>
       </c>
       <c r="D152" t="n">
         <v>151</v>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2.331876477399435</v>
+        <v>0.7270838924127058</v>
       </c>
       <c r="D153" t="n">
         <v>152</v>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>LSC-33</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2.342495426879799</v>
+        <v>0.7273672287322295</v>
       </c>
       <c r="D154" t="n">
         <v>153</v>
@@ -2899,11 +2899,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2.345119257307775</v>
+        <v>0.728482861081972</v>
       </c>
       <c r="D155" t="n">
         <v>154</v>
@@ -2915,11 +2915,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2.354622465982963</v>
+        <v>0.7291709761740622</v>
       </c>
       <c r="D156" t="n">
         <v>155</v>
@@ -2931,11 +2931,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2.374797188301778</v>
+        <v>0.7291940360216314</v>
       </c>
       <c r="D157" t="n">
         <v>156</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2.386608600933051</v>
+        <v>0.7307420147438223</v>
       </c>
       <c r="D158" t="n">
         <v>157</v>
@@ -2963,11 +2963,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2.404075708339076</v>
+        <v>0.7316955359671756</v>
       </c>
       <c r="D159" t="n">
         <v>158</v>
@@ -2979,11 +2979,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2.426258453264439</v>
+        <v>0.733380652188492</v>
       </c>
       <c r="D160" t="n">
         <v>159</v>
@@ -2995,11 +2995,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>LSC-63</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2.447053049583766</v>
+        <v>0.7339913649425773</v>
       </c>
       <c r="D161" t="n">
         <v>160</v>
@@ -3011,11 +3011,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2.462421000713577</v>
+        <v>0.7343685155276131</v>
       </c>
       <c r="D162" t="n">
         <v>161</v>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>DR-147</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2.479427488290719</v>
+        <v>0.7373706302091109</v>
       </c>
       <c r="D163" t="n">
         <v>162</v>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2.490543804887305</v>
+        <v>0.7374857745814903</v>
       </c>
       <c r="D164" t="n">
         <v>163</v>
@@ -3059,11 +3059,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2.496300783960359</v>
+        <v>0.7377077498112499</v>
       </c>
       <c r="D165" t="n">
         <v>164</v>
@@ -3075,11 +3075,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2.519851425934307</v>
+        <v>0.7379565237802633</v>
       </c>
       <c r="D166" t="n">
         <v>165</v>
@@ -3091,11 +3091,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2.533528760030684</v>
+        <v>0.7383848285456238</v>
       </c>
       <c r="D167" t="n">
         <v>166</v>
@@ -3107,11 +3107,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2.572324085095787</v>
+        <v>0.7399778014391581</v>
       </c>
       <c r="D168" t="n">
         <v>167</v>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>SCR-07</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2.640973257360858</v>
+        <v>0.7402204641900354</v>
       </c>
       <c r="D169" t="n">
         <v>168</v>
@@ -3139,11 +3139,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2.644770402642359</v>
+        <v>0.7406005933931757</v>
       </c>
       <c r="D170" t="n">
         <v>169</v>
@@ -3155,11 +3155,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2.689290658553455</v>
+        <v>0.7408530584066604</v>
       </c>
       <c r="D171" t="n">
         <v>170</v>
@@ -3171,11 +3171,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2.74901437268143</v>
+        <v>0.7424813338234342</v>
       </c>
       <c r="D172" t="n">
         <v>171</v>
@@ -3187,11 +3187,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2.760509079714799</v>
+        <v>0.7434927970661049</v>
       </c>
       <c r="D173" t="n">
         <v>172</v>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2.763479807123514</v>
+        <v>0.7435462509186141</v>
       </c>
       <c r="D174" t="n">
         <v>173</v>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2.828166794916441</v>
+        <v>0.7450014636331211</v>
       </c>
       <c r="D175" t="n">
         <v>174</v>
@@ -3235,11 +3235,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>LSC-31</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2.831748300360889</v>
+        <v>0.7453593990769678</v>
       </c>
       <c r="D176" t="n">
         <v>175</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>LSC-50</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2.84582826505566</v>
+        <v>0.7453688987096825</v>
       </c>
       <c r="D177" t="n">
         <v>176</v>
@@ -3267,11 +3267,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2.867646459747699</v>
+        <v>0.7455884373613997</v>
       </c>
       <c r="D178" t="n">
         <v>177</v>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2.890769349844495</v>
+        <v>0.7456115276744687</v>
       </c>
       <c r="D179" t="n">
         <v>178</v>
@@ -3299,11 +3299,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2.89246897692229</v>
+        <v>0.7457406841854888</v>
       </c>
       <c r="D180" t="n">
         <v>179</v>
@@ -3315,11 +3315,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2.917489125100054</v>
+        <v>0.7462759345501352</v>
       </c>
       <c r="D181" t="n">
         <v>180</v>
@@ -3331,11 +3331,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2.924915352577265</v>
+        <v>0.7465478770908068</v>
       </c>
       <c r="D182" t="n">
         <v>181</v>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>LSC-35</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2.951036662966345</v>
+        <v>0.7472603082367389</v>
       </c>
       <c r="D183" t="n">
         <v>182</v>
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>LSC-44</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2.96181698670493</v>
+        <v>0.7474385555488232</v>
       </c>
       <c r="D184" t="n">
         <v>183</v>
@@ -3379,11 +3379,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2.963231493334849</v>
+        <v>0.7484636277547073</v>
       </c>
       <c r="D185" t="n">
         <v>184</v>
@@ -3395,11 +3395,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2.980226863603674</v>
+        <v>0.749377485944159</v>
       </c>
       <c r="D186" t="n">
         <v>185</v>
@@ -3411,11 +3411,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2.981908648169002</v>
+        <v>0.7502874870054808</v>
       </c>
       <c r="D187" t="n">
         <v>186</v>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2.993905594326431</v>
+        <v>0.7506369735077173</v>
       </c>
       <c r="D188" t="n">
         <v>187</v>
@@ -3443,11 +3443,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>LSC-34</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3.008968663813961</v>
+        <v>0.7514999894689889</v>
       </c>
       <c r="D189" t="n">
         <v>188</v>
@@ -3459,11 +3459,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>DR-158</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3.029942607617384</v>
+        <v>0.753987481255169</v>
       </c>
       <c r="D190" t="n">
         <v>189</v>
@@ -3475,11 +3475,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>LSC-49</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3.102842087588441</v>
+        <v>0.7548875000535075</v>
       </c>
       <c r="D191" t="n">
         <v>190</v>
@@ -3491,11 +3491,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3.144907615587742</v>
+        <v>0.755283620274248</v>
       </c>
       <c r="D192" t="n">
         <v>191</v>
@@ -3507,11 +3507,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>DR-151</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3.201937143472751</v>
+        <v>0.7565779639736593</v>
       </c>
       <c r="D193" t="n">
         <v>192</v>
@@ -3523,11 +3523,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3.216623186227426</v>
+        <v>0.7565805411995415</v>
       </c>
       <c r="D194" t="n">
         <v>193</v>
@@ -3539,11 +3539,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DR-154</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3.221471462810959</v>
+        <v>0.7583025366794888</v>
       </c>
       <c r="D195" t="n">
         <v>194</v>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3.302504865988261</v>
+        <v>0.762404848086445</v>
       </c>
       <c r="D196" t="n">
         <v>195</v>
@@ -3571,11 +3571,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3.308387244945979</v>
+        <v>0.7646378735076567</v>
       </c>
       <c r="D197" t="n">
         <v>196</v>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3.342005881826272</v>
+        <v>0.7715062519803992</v>
       </c>
       <c r="D198" t="n">
         <v>197</v>
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>3.362997082671668</v>
+        <v>0.7741729333826303</v>
       </c>
       <c r="D199" t="n">
         <v>198</v>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>LSC-20</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3.388877017626667</v>
+        <v>0.7748574892518508</v>
       </c>
       <c r="D200" t="n">
         <v>199</v>
@@ -3635,11 +3635,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3.406731806065343</v>
+        <v>0.7761865256035769</v>
       </c>
       <c r="D201" t="n">
         <v>200</v>
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>DR-149</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>3.419836466439655</v>
+        <v>0.7829071532961724</v>
       </c>
       <c r="D202" t="n">
         <v>201</v>
@@ -3667,11 +3667,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>DR-146</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3.441225940226508</v>
+        <v>0.7847547521283286</v>
       </c>
       <c r="D203" t="n">
         <v>202</v>
@@ -3683,11 +3683,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>3.471640522215216</v>
+        <v>0.7901126219853953</v>
       </c>
       <c r="D204" t="n">
         <v>203</v>
@@ -3699,11 +3699,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3.496490641299062</v>
+        <v>0.7927529410728149</v>
       </c>
       <c r="D205" t="n">
         <v>204</v>
@@ -3715,11 +3715,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>3.513996231819244</v>
+        <v>0.7949238742549297</v>
       </c>
       <c r="D206" t="n">
         <v>205</v>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>3.55318567121627</v>
+        <v>0.8053803179439509</v>
       </c>
       <c r="D207" t="n">
         <v>206</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>3.557871964241698</v>
+        <v>0.8057876058594206</v>
       </c>
       <c r="D208" t="n">
         <v>207</v>
@@ -3763,11 +3763,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>3.628259546920428</v>
+        <v>0.8074827057650966</v>
       </c>
       <c r="D209" t="n">
         <v>208</v>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3.650971145561097</v>
+        <v>0.8075787645323061</v>
       </c>
       <c r="D210" t="n">
         <v>209</v>
@@ -3795,11 +3795,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3.660881940237104</v>
+        <v>0.808120906612069</v>
       </c>
       <c r="D211" t="n">
         <v>210</v>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3.67803512406718</v>
+        <v>0.8085846529297001</v>
       </c>
       <c r="D212" t="n">
         <v>211</v>
@@ -3827,11 +3827,11 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>3.681838434817529</v>
+        <v>0.8155236609032696</v>
       </c>
       <c r="D213" t="n">
         <v>212</v>
@@ -3843,11 +3843,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3.738640352011697</v>
+        <v>0.8168103052625093</v>
       </c>
       <c r="D214" t="n">
         <v>213</v>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3.831779336136942</v>
+        <v>0.8170351109217519</v>
       </c>
       <c r="D215" t="n">
         <v>214</v>
@@ -3875,11 +3875,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3.859064533468148</v>
+        <v>0.8170891898991728</v>
       </c>
       <c r="D216" t="n">
         <v>215</v>
@@ -3891,11 +3891,11 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3.882269467735987</v>
+        <v>0.8173976154216486</v>
       </c>
       <c r="D217" t="n">
         <v>216</v>
@@ -3907,11 +3907,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>SCR-05</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3.927630929673222</v>
+        <v>0.8179387607603645</v>
       </c>
       <c r="D218" t="n">
         <v>217</v>
@@ -3923,11 +3923,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3.975472939029722</v>
+        <v>0.8187960522111127</v>
       </c>
       <c r="D219" t="n">
         <v>218</v>
@@ -3939,11 +3939,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>4.113098870499632</v>
+        <v>0.8217537278579796</v>
       </c>
       <c r="D220" t="n">
         <v>219</v>
@@ -3955,11 +3955,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>4.234344600914814</v>
+        <v>0.8234933562974832</v>
       </c>
       <c r="D221" t="n">
         <v>220</v>
@@ -3971,11 +3971,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>4.253570297804814</v>
+        <v>0.8252447264562904</v>
       </c>
       <c r="D222" t="n">
         <v>221</v>
@@ -3987,11 +3987,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>4.292117288815221</v>
+        <v>0.8257273107589458</v>
       </c>
       <c r="D223" t="n">
         <v>222</v>
@@ -4003,11 +4003,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>4.314021542726616</v>
+        <v>0.8276399801737792</v>
       </c>
       <c r="D224" t="n">
         <v>223</v>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>4.391681541309022</v>
+        <v>0.8292463579322019</v>
       </c>
       <c r="D225" t="n">
         <v>224</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>4.468968995683205</v>
+        <v>0.8300937438114662</v>
       </c>
       <c r="D226" t="n">
         <v>225</v>
@@ -4051,11 +4051,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>4.537863287148288</v>
+        <v>0.8318067580495626</v>
       </c>
       <c r="D227" t="n">
         <v>226</v>
@@ -4067,11 +4067,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>4.641127841209785</v>
+        <v>0.8323092860483637</v>
       </c>
       <c r="D228" t="n">
         <v>227</v>
@@ -4083,11 +4083,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>5.165385367077522</v>
+        <v>0.832417996810382</v>
       </c>
       <c r="D229" t="n">
         <v>228</v>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>5.600905185773277</v>
+        <v>0.8331029990316078</v>
       </c>
       <c r="D230" t="n">
         <v>229</v>
@@ -4115,11 +4115,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>5.994649004624828</v>
+        <v>0.8342771037256772</v>
       </c>
       <c r="D231" t="n">
         <v>230</v>
@@ -4131,11 +4131,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>6.555506950144018</v>
+        <v>0.8367155983650418</v>
       </c>
       <c r="D232" t="n">
         <v>231</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>6.721331834074801</v>
+        <v>0.8368231194644373</v>
       </c>
       <c r="D233" t="n">
         <v>232</v>
@@ -4163,14 +4163,1246 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>6.842172179612913</v>
+        <v>0.8388221221641986</v>
       </c>
       <c r="D234" t="n">
         <v>233</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DR-180</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>0.839265102285905</v>
+      </c>
+      <c r="D235" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DR-205</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0.8405493901126285</v>
+      </c>
+      <c r="D236" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DR-77</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>0.8406595376757695</v>
+      </c>
+      <c r="D237" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DR-97</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>0.841367819168973</v>
+      </c>
+      <c r="D238" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>DR-101</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>0.8419619812886378</v>
+      </c>
+      <c r="D239" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DR-124</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>0.8432682668420505</v>
+      </c>
+      <c r="D240" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DR-55</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>0.8434316473042559</v>
+      </c>
+      <c r="D241" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>DR-184</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>0.8435777400629513</v>
+      </c>
+      <c r="D242" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DR-139</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>0.8435840614024143</v>
+      </c>
+      <c r="D243" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>DR-107</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>0.8436844180598873</v>
+      </c>
+      <c r="D244" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>LSC-64</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>0.8453296883576514</v>
+      </c>
+      <c r="D245" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>DR-83</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>0.8461714672265884</v>
+      </c>
+      <c r="D246" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DR-75</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>0.8462693821907202</v>
+      </c>
+      <c r="D247" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DR-93</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>0.8474154038557525</v>
+      </c>
+      <c r="D248" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>DR-91</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>0.8475734038315531</v>
+      </c>
+      <c r="D249" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>DR-135</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>0.8500737697541936</v>
+      </c>
+      <c r="D250" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>DR-68</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>0.8501716975545801</v>
+      </c>
+      <c r="D251" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>DR-96</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>0.8515926337888647</v>
+      </c>
+      <c r="D252" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>DR-86</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0.8523789511894414</v>
+      </c>
+      <c r="D253" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DR-105</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0.8526764499528023</v>
+      </c>
+      <c r="D254" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>DR-79</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>0.852779664356597</v>
+      </c>
+      <c r="D255" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>DR-78</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>0.8543860196221917</v>
+      </c>
+      <c r="D256" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>DR-99</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>0.8550075123905827</v>
+      </c>
+      <c r="D257" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>DR-104</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>0.8553907866032717</v>
+      </c>
+      <c r="D258" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>DR-69</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>0.8558235024846439</v>
+      </c>
+      <c r="D259" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>DR-61</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>0.8569812492352644</v>
+      </c>
+      <c r="D260" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>DR-110</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>0.8595283050724688</v>
+      </c>
+      <c r="D261" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>DR-06</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>0.8597500425092688</v>
+      </c>
+      <c r="D262" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>DR-72</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>0.860134173182138</v>
+      </c>
+      <c r="D263" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>DR-132</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>0.8610267109979143</v>
+      </c>
+      <c r="D264" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>DR-224</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>0.8624406032484547</v>
+      </c>
+      <c r="D265" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>DR-58</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>0.8684353573915103</v>
+      </c>
+      <c r="D266" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>DR-128</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>0.8701870204207891</v>
+      </c>
+      <c r="D267" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>DR-218</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>0.8739169428533896</v>
+      </c>
+      <c r="D268" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>DR-125</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>0.87501059591394</v>
+      </c>
+      <c r="D269" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>DR-02</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>0.875428368862209</v>
+      </c>
+      <c r="D270" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>DR-66</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>0.8767529786582693</v>
+      </c>
+      <c r="D271" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>DR-117</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>0.878154107311422</v>
+      </c>
+      <c r="D272" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>DR-134</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>0.8781877825772471</v>
+      </c>
+      <c r="D273" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>DR-67</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>0.8787512684729608</v>
+      </c>
+      <c r="D274" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>DR-115</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>0.8840720227167302</v>
+      </c>
+      <c r="D275" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>DR-116</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>0.8861454020522673</v>
+      </c>
+      <c r="D276" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>275</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>DR-87</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>0.8865008629440071</v>
+      </c>
+      <c r="D277" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>DR-07</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0.8867706269128066</v>
+      </c>
+      <c r="D278" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>DR-82</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>0.8910190354429394</v>
+      </c>
+      <c r="D279" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>278</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>DR-219</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>0.8918547235437025</v>
+      </c>
+      <c r="D280" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>DR-13</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>0.8925394350711079</v>
+      </c>
+      <c r="D281" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>DR-119</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>0.8930400949016023</v>
+      </c>
+      <c r="D282" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>DR-113</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>0.8943665637586663</v>
+      </c>
+      <c r="D283" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>282</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>DR-102</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>0.896077374201509</v>
+      </c>
+      <c r="D284" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>DR-46</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>0.8993842824057231</v>
+      </c>
+      <c r="D285" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>DR-106</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>0.902094664955028</v>
+      </c>
+      <c r="D286" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>DR-62</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>0.9023435681064832</v>
+      </c>
+      <c r="D287" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>DR-122</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>0.9066027348882969</v>
+      </c>
+      <c r="D288" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>LSC-21</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>0.9076740501985733</v>
+      </c>
+      <c r="D289" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>DR-215</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>0.914736808914428</v>
+      </c>
+      <c r="D290" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>DR-90</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>0.9154981860236623</v>
+      </c>
+      <c r="D291" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>DR-161</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>0.915839719452416</v>
+      </c>
+      <c r="D292" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>DR-211</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>0.9204349152407724</v>
+      </c>
+      <c r="D293" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>DR-60</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>0.9217139565678142</v>
+      </c>
+      <c r="D294" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>DR-34</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>0.9246854244831948</v>
+      </c>
+      <c r="D295" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>DR-92</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>0.9252587478102722</v>
+      </c>
+      <c r="D296" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>DR-114</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>0.9305019458373391</v>
+      </c>
+      <c r="D297" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>296</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>LSC-11</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>0.9418960625367413</v>
+      </c>
+      <c r="D298" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>297</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>DR-73</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>0.9465494949833665</v>
+      </c>
+      <c r="D299" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>298</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>LSC-67</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>0.9470495324278043</v>
+      </c>
+      <c r="D300" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>DR-84</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>0.949082603135816</v>
+      </c>
+      <c r="D301" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>DR-81</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>0.950470872602708</v>
+      </c>
+      <c r="D302" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>DR-138</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>0.9584387621757808</v>
+      </c>
+      <c r="D303" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>302</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>DR-80</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>0.9631340526476359</v>
+      </c>
+      <c r="D304" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>303</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>DR-70</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>0.9810530253169335</v>
+      </c>
+      <c r="D305" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>DR-64</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>0.9825899486763504</v>
+      </c>
+      <c r="D306" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>DR-234</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>0.9867629327403485</v>
+      </c>
+      <c r="D307" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>306</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>DR-118</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>1</v>
+      </c>
+      <c r="D308" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>307</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>DR-111</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>1</v>
+      </c>
+      <c r="D309" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>308</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>DR-187</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>1</v>
+      </c>
+      <c r="D310" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>309</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>DR-120</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" t="n">
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/PCA_Stressors/tables/MaxRel_site_rankings.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/MaxRel_site_rankings.xlsx
@@ -451,11 +451,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3462664435142515</v>
+        <v>0.2439477119021697</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -467,11 +467,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3496776445458151</v>
+        <v>0.2802646001959314</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3797930998848826</v>
+        <v>0.2823796085202896</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -499,11 +499,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3953345663194837</v>
+        <v>0.2831696071905873</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -515,11 +515,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4274371806522259</v>
+        <v>0.2904621462754347</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -531,11 +531,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.4297337860557036</v>
+        <v>0.2907720881073051</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -547,11 +547,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4323533622575924</v>
+        <v>0.3120260853741085</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -563,11 +563,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DR-52</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4444414212074977</v>
+        <v>0.3159059478543164</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -579,11 +579,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4464897872875588</v>
+        <v>0.3228453403317631</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -595,11 +595,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.4576832611049282</v>
+        <v>0.3233551894010563</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -611,11 +611,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.458149766195094</v>
+        <v>0.3235964686314858</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -627,11 +627,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4692844653483959</v>
+        <v>0.3273171759443609</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -643,11 +643,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4708173402063078</v>
+        <v>0.3284647290669116</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
@@ -659,11 +659,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4715512418627715</v>
+        <v>0.3310943878555366</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DR-30</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.4729255558296746</v>
+        <v>0.3334699857641057</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -691,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4775085652735411</v>
+        <v>0.3341789515328611</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -707,11 +707,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DR-98</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4787220558854894</v>
+        <v>0.3384807798203809</v>
       </c>
       <c r="D18" t="n">
         <v>17</v>
@@ -723,11 +723,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DR-169</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4816654691901178</v>
+        <v>0.3388894314085624</v>
       </c>
       <c r="D19" t="n">
         <v>18</v>
@@ -739,11 +739,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DR-201</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4900975712348741</v>
+        <v>0.3395578633276396</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
@@ -755,11 +755,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5022633860461179</v>
+        <v>0.3399346780943617</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
@@ -771,11 +771,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.5045175164105158</v>
+        <v>0.3403015581916689</v>
       </c>
       <c r="D22" t="n">
         <v>21</v>
@@ -787,11 +787,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.509303522998426</v>
+        <v>0.3423161588458564</v>
       </c>
       <c r="D23" t="n">
         <v>22</v>
@@ -803,11 +803,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.5144833254877228</v>
+        <v>0.3432515416414838</v>
       </c>
       <c r="D24" t="n">
         <v>23</v>
@@ -819,11 +819,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.5150666365022126</v>
+        <v>0.3432736113489012</v>
       </c>
       <c r="D25" t="n">
         <v>24</v>
@@ -835,11 +835,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DR-231</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.5153620397658929</v>
+        <v>0.3451901441393232</v>
       </c>
       <c r="D26" t="n">
         <v>25</v>
@@ -851,11 +851,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.5179081261241051</v>
+        <v>0.3464645126388147</v>
       </c>
       <c r="D27" t="n">
         <v>26</v>
@@ -867,11 +867,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.5211362625251322</v>
+        <v>0.3464967736766528</v>
       </c>
       <c r="D28" t="n">
         <v>27</v>
@@ -883,11 +883,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DR-57</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.5242655307301869</v>
+        <v>0.3469714747413358</v>
       </c>
       <c r="D29" t="n">
         <v>28</v>
@@ -899,11 +899,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DR-12</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.535477548742438</v>
+        <v>0.3540311572390903</v>
       </c>
       <c r="D30" t="n">
         <v>29</v>
@@ -915,11 +915,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DR-28</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.5373798236202265</v>
+        <v>0.3591032591649929</v>
       </c>
       <c r="D31" t="n">
         <v>30</v>
@@ -931,11 +931,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.5401328628551662</v>
+        <v>0.3639595565036993</v>
       </c>
       <c r="D32" t="n">
         <v>31</v>
@@ -947,11 +947,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DR-42</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.5403383870452557</v>
+        <v>0.3696975620019934</v>
       </c>
       <c r="D33" t="n">
         <v>32</v>
@@ -963,11 +963,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.5405769473162717</v>
+        <v>0.3705120024382922</v>
       </c>
       <c r="D34" t="n">
         <v>33</v>
@@ -979,11 +979,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.5429295692833933</v>
+        <v>0.3791545589286053</v>
       </c>
       <c r="D35" t="n">
         <v>34</v>
@@ -995,11 +995,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DR-43</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.543273883175983</v>
+        <v>0.3810146908705792</v>
       </c>
       <c r="D36" t="n">
         <v>35</v>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DR-24</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.5446988021022459</v>
+        <v>0.3820683337340421</v>
       </c>
       <c r="D37" t="n">
         <v>36</v>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DR-08</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.5486565835616674</v>
+        <v>0.3840904991901393</v>
       </c>
       <c r="D38" t="n">
         <v>37</v>
@@ -1043,11 +1043,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.5557877595112918</v>
+        <v>0.3855101410955</v>
       </c>
       <c r="D39" t="n">
         <v>38</v>
@@ -1059,11 +1059,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DR-153</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.5603453196095525</v>
+        <v>0.387291462423519</v>
       </c>
       <c r="D40" t="n">
         <v>39</v>
@@ -1075,11 +1075,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DR-191</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.5676893132633262</v>
+        <v>0.3927835442838117</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DR-41</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.5699832652486376</v>
+        <v>0.3933757799833529</v>
       </c>
       <c r="D42" t="n">
         <v>41</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DR-232</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.572305892231565</v>
+        <v>0.3956912381175047</v>
       </c>
       <c r="D43" t="n">
         <v>42</v>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DR-165</t>
+          <t>LSC-31</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.5744284821124763</v>
+        <v>0.3999480443414548</v>
       </c>
       <c r="D44" t="n">
         <v>43</v>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DR-142</t>
+          <t>DR-156</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.5786790716722673</v>
+        <v>0.4094453699367821</v>
       </c>
       <c r="D45" t="n">
         <v>44</v>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.5864290829592963</v>
+        <v>0.4095037832863439</v>
       </c>
       <c r="D46" t="n">
         <v>45</v>
@@ -1171,11 +1171,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DR-157</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.586468408188435</v>
+        <v>0.4104549665429617</v>
       </c>
       <c r="D47" t="n">
         <v>46</v>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DR-29</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.5977184367277821</v>
+        <v>0.4122103752854776</v>
       </c>
       <c r="D48" t="n">
         <v>47</v>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DR-196</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.5980999040592121</v>
+        <v>0.4125725020819695</v>
       </c>
       <c r="D49" t="n">
         <v>48</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.599367293516583</v>
+        <v>0.4147258974845272</v>
       </c>
       <c r="D50" t="n">
         <v>49</v>
@@ -1235,11 +1235,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DR-148</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.6001254785412375</v>
+        <v>0.4155965992801489</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DR-199</t>
+          <t>LSC-35</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.6061398275077845</v>
+        <v>0.4195729738042295</v>
       </c>
       <c r="D52" t="n">
         <v>51</v>
@@ -1267,11 +1267,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DR-35</t>
+          <t>LSC-29</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.6076758252386268</v>
+        <v>0.4225340109174404</v>
       </c>
       <c r="D53" t="n">
         <v>52</v>
@@ -1283,11 +1283,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DR-36</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.6136105454847579</v>
+        <v>0.4331825090609171</v>
       </c>
       <c r="D54" t="n">
         <v>53</v>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DR-03</t>
+          <t>DR-155</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.6151889609011129</v>
+        <v>0.4343320456330388</v>
       </c>
       <c r="D55" t="n">
         <v>54</v>
@@ -1315,11 +1315,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SCR-13</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.6177431158635652</v>
+        <v>0.4349065880394938</v>
       </c>
       <c r="D56" t="n">
         <v>55</v>
@@ -1331,11 +1331,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DR-193</t>
+          <t>LSC-51</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.6224788783341002</v>
+        <v>0.4372641082974943</v>
       </c>
       <c r="D57" t="n">
         <v>56</v>
@@ -1347,11 +1347,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DR-233</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.6235231547056608</v>
+        <v>0.4375885457759749</v>
       </c>
       <c r="D58" t="n">
         <v>57</v>
@@ -1363,11 +1363,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DR-200</t>
+          <t>LSC-52</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.6236700881102278</v>
+        <v>0.4377869618068105</v>
       </c>
       <c r="D59" t="n">
         <v>58</v>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DR-16</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.62521936092718</v>
+        <v>0.4415650702913582</v>
       </c>
       <c r="D60" t="n">
         <v>59</v>
@@ -1395,11 +1395,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DR-230</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.6264430050939052</v>
+        <v>0.4456504125660498</v>
       </c>
       <c r="D61" t="n">
         <v>60</v>
@@ -1411,11 +1411,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.6320240906632355</v>
+        <v>0.4480735290494902</v>
       </c>
       <c r="D62" t="n">
         <v>61</v>
@@ -1427,11 +1427,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DR-235</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.6330377273190512</v>
+        <v>0.4483305676019988</v>
       </c>
       <c r="D63" t="n">
         <v>62</v>
@@ -1443,11 +1443,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DR-178</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.6335103192287275</v>
+        <v>0.4556113109810385</v>
       </c>
       <c r="D64" t="n">
         <v>63</v>
@@ -1459,11 +1459,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DR-189</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.6372522329272635</v>
+        <v>0.4567102165869878</v>
       </c>
       <c r="D65" t="n">
         <v>64</v>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DR-227</t>
+          <t>LSC-33</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.6375697175070046</v>
+        <v>0.4645215191652897</v>
       </c>
       <c r="D66" t="n">
         <v>65</v>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-46</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.6379846389462813</v>
+        <v>0.467184030242317</v>
       </c>
       <c r="D67" t="n">
         <v>66</v>
@@ -1507,11 +1507,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LSC-36</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.6385451469597292</v>
+        <v>0.4721396018782881</v>
       </c>
       <c r="D68" t="n">
         <v>67</v>
@@ -1523,11 +1523,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DR-226</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.63962072753053</v>
+        <v>0.4771812681205495</v>
       </c>
       <c r="D69" t="n">
         <v>68</v>
@@ -1539,11 +1539,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DR-39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.6463420735679341</v>
+        <v>0.4796932316905573</v>
       </c>
       <c r="D70" t="n">
         <v>69</v>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>DR-146</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.6493889968254914</v>
+        <v>0.495325788433252</v>
       </c>
       <c r="D71" t="n">
         <v>70</v>
@@ -1571,11 +1571,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SCR-10</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.649827934219272</v>
+        <v>0.499410849214198</v>
       </c>
       <c r="D72" t="n">
         <v>71</v>
@@ -1587,11 +1587,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DR-223</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.6568404026702845</v>
+        <v>0.5010293243644689</v>
       </c>
       <c r="D73" t="n">
         <v>72</v>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DR-26</t>
+          <t>LSC-61</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.6572643504002024</v>
+        <v>0.502092156030338</v>
       </c>
       <c r="D74" t="n">
         <v>73</v>
@@ -1619,11 +1619,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DR-214</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.6584238892571777</v>
+        <v>0.5054237587955491</v>
       </c>
       <c r="D75" t="n">
         <v>74</v>
@@ -1635,11 +1635,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DR-150</t>
+          <t>LSC-28</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.6596319478791576</v>
+        <v>0.5080080256510843</v>
       </c>
       <c r="D76" t="n">
         <v>75</v>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-63</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.6610357787448649</v>
+        <v>0.5106788659085415</v>
       </c>
       <c r="D77" t="n">
         <v>76</v>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LSC-28</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.6628233064264522</v>
+        <v>0.5174292746422217</v>
       </c>
       <c r="D78" t="n">
         <v>77</v>
@@ -1683,11 +1683,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DR-25</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.6634947298958765</v>
+        <v>0.5179555453677822</v>
       </c>
       <c r="D79" t="n">
         <v>78</v>
@@ -1699,11 +1699,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>LSC-54</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.6642859200112887</v>
+        <v>0.5190196655440519</v>
       </c>
       <c r="D80" t="n">
         <v>79</v>
@@ -1715,11 +1715,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DR-27</t>
+          <t>LSC-36</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.6652982584732056</v>
+        <v>0.5198970723200464</v>
       </c>
       <c r="D81" t="n">
         <v>80</v>
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DR-222</t>
+          <t>DR-149</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.6670386647178785</v>
+        <v>0.5280907115112188</v>
       </c>
       <c r="D82" t="n">
         <v>81</v>
@@ -1747,11 +1747,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LSC-65</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.6714622266199197</v>
+        <v>0.5321698653523285</v>
       </c>
       <c r="D83" t="n">
         <v>82</v>
@@ -1763,11 +1763,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.6727244975258698</v>
+        <v>0.5324767069103575</v>
       </c>
       <c r="D84" t="n">
         <v>83</v>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DR-228</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.6735729211664</v>
+        <v>0.5336416573073904</v>
       </c>
       <c r="D85" t="n">
         <v>84</v>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>LSC-34</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.6759971933216478</v>
+        <v>0.5386339311537593</v>
       </c>
       <c r="D86" t="n">
         <v>85</v>
@@ -1811,11 +1811,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SCR-12</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.6767709009360195</v>
+        <v>0.5387281474231385</v>
       </c>
       <c r="D87" t="n">
         <v>86</v>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DR-198</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.677158075652446</v>
+        <v>0.5425949249179378</v>
       </c>
       <c r="D88" t="n">
         <v>87</v>
@@ -1843,11 +1843,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>SCR-07</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.6781982309307213</v>
+        <v>0.5469904154977991</v>
       </c>
       <c r="D89" t="n">
         <v>88</v>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.6786659525735743</v>
+        <v>0.5483731343174977</v>
       </c>
       <c r="D90" t="n">
         <v>89</v>
@@ -1875,11 +1875,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SCR-16</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.6787130942897357</v>
+        <v>0.5494515934792212</v>
       </c>
       <c r="D91" t="n">
         <v>90</v>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DR-182</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.6794235773022457</v>
+        <v>0.5564078044288699</v>
       </c>
       <c r="D92" t="n">
         <v>91</v>
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.6816214642310559</v>
+        <v>0.5582473955340463</v>
       </c>
       <c r="D93" t="n">
         <v>92</v>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DR-155</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.6820658159350247</v>
+        <v>0.5611720488984752</v>
       </c>
       <c r="D94" t="n">
         <v>93</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.6825596691810616</v>
+        <v>0.5680896454255198</v>
       </c>
       <c r="D95" t="n">
         <v>94</v>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DR-194</t>
+          <t>DR-58</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.6839651506591352</v>
+        <v>0.5686614232629905</v>
       </c>
       <c r="D96" t="n">
         <v>95</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-50</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.6862662803391393</v>
+        <v>0.569015743562865</v>
       </c>
       <c r="D97" t="n">
         <v>96</v>
@@ -1987,11 +1987,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DR-37</t>
+          <t>DR-96</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.6871039479750344</v>
+        <v>0.5714902042287563</v>
       </c>
       <c r="D98" t="n">
         <v>97</v>
@@ -2003,11 +2003,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LSC-52</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.6879323295104336</v>
+        <v>0.5719735593955085</v>
       </c>
       <c r="D99" t="n">
         <v>98</v>
@@ -2019,11 +2019,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.6883530825580165</v>
+        <v>0.5754495562923118</v>
       </c>
       <c r="D100" t="n">
         <v>99</v>
@@ -2035,11 +2035,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LSC-46</t>
+          <t>LSC-44</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.688946470309342</v>
+        <v>0.576126620845773</v>
       </c>
       <c r="D101" t="n">
         <v>100</v>
@@ -2051,11 +2051,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.6891259922174557</v>
+        <v>0.5768499294315204</v>
       </c>
       <c r="D102" t="n">
         <v>101</v>
@@ -2067,11 +2067,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.6901307836523848</v>
+        <v>0.5792004403837515</v>
       </c>
       <c r="D103" t="n">
         <v>102</v>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.6907225076894121</v>
+        <v>0.5793523495091775</v>
       </c>
       <c r="D104" t="n">
         <v>103</v>
@@ -2099,11 +2099,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DR-171</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.6910592667626752</v>
+        <v>0.5794160362062324</v>
       </c>
       <c r="D105" t="n">
         <v>104</v>
@@ -2115,11 +2115,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.6912858326251796</v>
+        <v>0.5815553696659904</v>
       </c>
       <c r="D106" t="n">
         <v>105</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-113</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.6921248468989928</v>
+        <v>0.5824319500948489</v>
       </c>
       <c r="D107" t="n">
         <v>106</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DR-225</t>
+          <t>DR-104</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.6929886330659415</v>
+        <v>0.5828467983283543</v>
       </c>
       <c r="D108" t="n">
         <v>107</v>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DR-203</t>
+          <t>LSC-66</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.6941403720124526</v>
+        <v>0.5955062568825138</v>
       </c>
       <c r="D109" t="n">
         <v>108</v>
@@ -2179,11 +2179,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.6944317164075668</v>
+        <v>0.6011734297386784</v>
       </c>
       <c r="D110" t="n">
         <v>109</v>
@@ -2195,11 +2195,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DR-22</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.6951348967947746</v>
+        <v>0.6049435802986112</v>
       </c>
       <c r="D111" t="n">
         <v>110</v>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DR-09</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.6953165687219887</v>
+        <v>0.6084925036477432</v>
       </c>
       <c r="D112" t="n">
         <v>111</v>
@@ -2227,11 +2227,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.6967083716077178</v>
+        <v>0.6097255686803082</v>
       </c>
       <c r="D113" t="n">
         <v>112</v>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.6968749626024541</v>
+        <v>0.6140130272932476</v>
       </c>
       <c r="D114" t="n">
         <v>113</v>
@@ -2259,11 +2259,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-20</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.6970599698633732</v>
+        <v>0.6171689816998087</v>
       </c>
       <c r="D115" t="n">
         <v>114</v>
@@ -2275,11 +2275,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-102</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.6975876019022981</v>
+        <v>0.6208496864908717</v>
       </c>
       <c r="D116" t="n">
         <v>115</v>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.6988239736851856</v>
+        <v>0.6283908440164194</v>
       </c>
       <c r="D117" t="n">
         <v>116</v>
@@ -2307,11 +2307,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DR-186</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.6989828294221436</v>
+        <v>0.6291664255992963</v>
       </c>
       <c r="D118" t="n">
         <v>117</v>
@@ -2323,11 +2323,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DR-159</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.6998952330351882</v>
+        <v>0.6303760454783708</v>
       </c>
       <c r="D119" t="n">
         <v>118</v>
@@ -2339,11 +2339,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DR-188</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.7001862130550459</v>
+        <v>0.6318916322195978</v>
       </c>
       <c r="D120" t="n">
         <v>119</v>
@@ -2355,11 +2355,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LSC-51</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.7002583724763561</v>
+        <v>0.6323823659752095</v>
       </c>
       <c r="D121" t="n">
         <v>120</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LSC-10</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.7010789395130795</v>
+        <v>0.632565636283921</v>
       </c>
       <c r="D122" t="n">
         <v>121</v>
@@ -2387,11 +2387,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DR-181</t>
+          <t>LSC-49</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.701591073475354</v>
+        <v>0.6334673745018378</v>
       </c>
       <c r="D123" t="n">
         <v>122</v>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.7027791599877119</v>
+        <v>0.6338745166561602</v>
       </c>
       <c r="D124" t="n">
         <v>123</v>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.7049071112370577</v>
+        <v>0.6345765032532266</v>
       </c>
       <c r="D125" t="n">
         <v>124</v>
@@ -2435,11 +2435,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DR-47</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.7051247739663712</v>
+        <v>0.637286234318088</v>
       </c>
       <c r="D126" t="n">
         <v>125</v>
@@ -2451,11 +2451,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DR-177</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.7067385526341784</v>
+        <v>0.638127699718705</v>
       </c>
       <c r="D127" t="n">
         <v>126</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.7073827715297302</v>
+        <v>0.6450046912880718</v>
       </c>
       <c r="D128" t="n">
         <v>127</v>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DR-11</t>
+          <t>DR-07</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.708180528446253</v>
+        <v>0.6452716128602287</v>
       </c>
       <c r="D129" t="n">
         <v>128</v>
@@ -2499,11 +2499,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.7089357009530139</v>
+        <v>0.6471310800416386</v>
       </c>
       <c r="D130" t="n">
         <v>129</v>
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.7129910633674774</v>
+        <v>0.6475602126392265</v>
       </c>
       <c r="D131" t="n">
         <v>130</v>
@@ -2531,11 +2531,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DR-221</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.7131379826387567</v>
+        <v>0.6476218914420823</v>
       </c>
       <c r="D132" t="n">
         <v>131</v>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.7141098707611813</v>
+        <v>0.6488262444913812</v>
       </c>
       <c r="D133" t="n">
         <v>132</v>
@@ -2563,11 +2563,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SCR-04</t>
+          <t>DR-107</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.7144824215235126</v>
+        <v>0.6497146680764767</v>
       </c>
       <c r="D134" t="n">
         <v>133</v>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.7145910395821197</v>
+        <v>0.6500440542718995</v>
       </c>
       <c r="D135" t="n">
         <v>134</v>
@@ -2595,11 +2595,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.7158177983131931</v>
+        <v>0.6501932042781203</v>
       </c>
       <c r="D136" t="n">
         <v>135</v>
@@ -2611,11 +2611,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LSC-61</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.7158750936210641</v>
+        <v>0.6504070204872784</v>
       </c>
       <c r="D137" t="n">
         <v>136</v>
@@ -2627,11 +2627,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.7169758132890097</v>
+        <v>0.6508023142407365</v>
       </c>
       <c r="D138" t="n">
         <v>137</v>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.7170522186918294</v>
+        <v>0.6564138399961255</v>
       </c>
       <c r="D139" t="n">
         <v>138</v>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LSC-12</t>
+          <t>DR-118</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.7171367419651229</v>
+        <v>0.658332469162474</v>
       </c>
       <c r="D140" t="n">
         <v>139</v>
@@ -2675,11 +2675,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LSC-29</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.7178469187412199</v>
+        <v>0.6587641422276826</v>
       </c>
       <c r="D141" t="n">
         <v>140</v>
@@ -2691,11 +2691,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.7185018930126073</v>
+        <v>0.6589441001560751</v>
       </c>
       <c r="D142" t="n">
         <v>141</v>
@@ -2707,11 +2707,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LSC-54</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.7190915119023116</v>
+        <v>0.6596353529857039</v>
       </c>
       <c r="D143" t="n">
         <v>142</v>
@@ -2723,11 +2723,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LSC-02</t>
+          <t>LSC-65</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.7210604300280651</v>
+        <v>0.6621276973740476</v>
       </c>
       <c r="D144" t="n">
         <v>143</v>
@@ -2739,11 +2739,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DR-156</t>
+          <t>DR-134</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.722596144817865</v>
+        <v>0.6636285422339627</v>
       </c>
       <c r="D145" t="n">
         <v>144</v>
@@ -2755,11 +2755,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DR-32</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.7231663103585916</v>
+        <v>0.6641741867871287</v>
       </c>
       <c r="D146" t="n">
         <v>145</v>
@@ -2771,11 +2771,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DR-31</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.7239428412631888</v>
+        <v>0.6644448884555034</v>
       </c>
       <c r="D147" t="n">
         <v>146</v>
@@ -2787,11 +2787,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LSC-66</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.7245351284672582</v>
+        <v>0.6646226981659191</v>
       </c>
       <c r="D148" t="n">
         <v>147</v>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LSC-01</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.7252582526111437</v>
+        <v>0.6653557470260405</v>
       </c>
       <c r="D149" t="n">
         <v>148</v>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.7259281554620718</v>
+        <v>0.6668681140948498</v>
       </c>
       <c r="D150" t="n">
         <v>149</v>
@@ -2835,11 +2835,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LSC-07</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.7262596168259837</v>
+        <v>0.6669262353540517</v>
       </c>
       <c r="D151" t="n">
         <v>150</v>
@@ -2851,11 +2851,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.726732807445975</v>
+        <v>0.6672217200491078</v>
       </c>
       <c r="D152" t="n">
         <v>151</v>
@@ -2867,11 +2867,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LSC-06</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.7270838924127058</v>
+        <v>0.6673373946767058</v>
       </c>
       <c r="D153" t="n">
         <v>152</v>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LSC-33</t>
+          <t>DR-97</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.7273672287322295</v>
+        <v>0.6674592360171663</v>
       </c>
       <c r="D154" t="n">
         <v>153</v>
@@ -2899,11 +2899,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.728482861081972</v>
+        <v>0.6696980435277423</v>
       </c>
       <c r="D155" t="n">
         <v>154</v>
@@ -2915,11 +2915,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.7291709761740622</v>
+        <v>0.6702660743513807</v>
       </c>
       <c r="D156" t="n">
         <v>155</v>
@@ -2931,11 +2931,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LSC-04</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>0.7291940360216314</v>
+        <v>0.67038016748981</v>
       </c>
       <c r="D157" t="n">
         <v>156</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SCR-02</t>
+          <t>DR-90</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0.7307420147438223</v>
+        <v>0.6712294940952355</v>
       </c>
       <c r="D158" t="n">
         <v>157</v>
@@ -2963,11 +2963,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SCR-15</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.7316955359671756</v>
+        <v>0.6723638926890185</v>
       </c>
       <c r="D159" t="n">
         <v>158</v>
@@ -2979,11 +2979,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LSC-03</t>
+          <t>DR-105</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0.733380652188492</v>
+        <v>0.6731169331430847</v>
       </c>
       <c r="D160" t="n">
         <v>159</v>
@@ -2995,11 +2995,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LSC-63</t>
+          <t>DR-161</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.7339913649425773</v>
+        <v>0.6747757575429606</v>
       </c>
       <c r="D161" t="n">
         <v>160</v>
@@ -3011,11 +3011,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DR-65</t>
+          <t>DR-13</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0.7343685155276131</v>
+        <v>0.6751621777226184</v>
       </c>
       <c r="D162" t="n">
         <v>161</v>
@@ -3027,11 +3027,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DR-147</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.7373706302091109</v>
+        <v>0.6759851538544565</v>
       </c>
       <c r="D163" t="n">
         <v>162</v>
@@ -3043,11 +3043,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DR-176</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.7374857745814903</v>
+        <v>0.6781757363623478</v>
       </c>
       <c r="D164" t="n">
         <v>163</v>
@@ -3059,11 +3059,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-180</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.7377077498112499</v>
+        <v>0.67896330803641</v>
       </c>
       <c r="D165" t="n">
         <v>164</v>
@@ -3075,11 +3075,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.7379565237802633</v>
+        <v>0.6791232114920023</v>
       </c>
       <c r="D166" t="n">
         <v>165</v>
@@ -3091,11 +3091,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.7383848285456238</v>
+        <v>0.6800751784641913</v>
       </c>
       <c r="D167" t="n">
         <v>166</v>
@@ -3107,11 +3107,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DR-76</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.7399778014391581</v>
+        <v>0.6805689963746022</v>
       </c>
       <c r="D168" t="n">
         <v>167</v>
@@ -3123,11 +3123,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SCR-07</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.7402204641900354</v>
+        <v>0.6811453951612144</v>
       </c>
       <c r="D169" t="n">
         <v>168</v>
@@ -3139,11 +3139,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.7406005933931757</v>
+        <v>0.6841580155383722</v>
       </c>
       <c r="D170" t="n">
         <v>169</v>
@@ -3155,11 +3155,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.7408530584066604</v>
+        <v>0.685448586631332</v>
       </c>
       <c r="D171" t="n">
         <v>170</v>
@@ -3171,11 +3171,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DR-33</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0.7424813338234342</v>
+        <v>0.6855342795332532</v>
       </c>
       <c r="D172" t="n">
         <v>171</v>
@@ -3187,11 +3187,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0.7434927970661049</v>
+        <v>0.6865336722361345</v>
       </c>
       <c r="D173" t="n">
         <v>172</v>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.7435462509186141</v>
+        <v>0.6866229831005926</v>
       </c>
       <c r="D174" t="n">
         <v>173</v>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.7450014636331211</v>
+        <v>0.6877658218215172</v>
       </c>
       <c r="D175" t="n">
         <v>174</v>
@@ -3235,11 +3235,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LSC-31</t>
+          <t>DR-106</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.7453593990769678</v>
+        <v>0.6915090218530723</v>
       </c>
       <c r="D176" t="n">
         <v>175</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LSC-50</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>0.7453688987096825</v>
+        <v>0.694608838604759</v>
       </c>
       <c r="D177" t="n">
         <v>176</v>
@@ -3267,11 +3267,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DR-212</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>0.7455884373613997</v>
+        <v>0.6946478291320304</v>
       </c>
       <c r="D178" t="n">
         <v>177</v>
@@ -3283,11 +3283,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DR-220</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.7456115276744687</v>
+        <v>0.7036752661178589</v>
       </c>
       <c r="D179" t="n">
         <v>178</v>
@@ -3299,11 +3299,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.7457406841854888</v>
+        <v>0.7056383501539292</v>
       </c>
       <c r="D180" t="n">
         <v>179</v>
@@ -3315,11 +3315,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.7462759345501352</v>
+        <v>0.7084536305736873</v>
       </c>
       <c r="D181" t="n">
         <v>180</v>
@@ -3331,11 +3331,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SCR-01</t>
+          <t>DR-116</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0.7465478770908068</v>
+        <v>0.7156664348514725</v>
       </c>
       <c r="D182" t="n">
         <v>181</v>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LSC-35</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.7472603082367389</v>
+        <v>0.7165326802620989</v>
       </c>
       <c r="D183" t="n">
         <v>182</v>
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LSC-44</t>
+          <t>DR-99</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.7474385555488232</v>
+        <v>0.717536583978628</v>
       </c>
       <c r="D184" t="n">
         <v>183</v>
@@ -3379,11 +3379,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DR-160</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.7484636277547073</v>
+        <v>0.7175987027952587</v>
       </c>
       <c r="D185" t="n">
         <v>184</v>
@@ -3395,11 +3395,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DR-21</t>
+          <t>DR-211</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.749377485944159</v>
+        <v>0.7210112964500029</v>
       </c>
       <c r="D186" t="n">
         <v>185</v>
@@ -3411,11 +3411,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DR-213</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0.7502874870054808</v>
+        <v>0.7212463265306178</v>
       </c>
       <c r="D187" t="n">
         <v>186</v>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>DR-158</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0.7506369735077173</v>
+        <v>0.7235853740430934</v>
       </c>
       <c r="D188" t="n">
         <v>187</v>
@@ -3443,11 +3443,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LSC-34</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.7514999894689889</v>
+        <v>0.7250700643150136</v>
       </c>
       <c r="D189" t="n">
         <v>188</v>
@@ -3459,11 +3459,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DR-158</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0.753987481255169</v>
+        <v>0.7266619070426266</v>
       </c>
       <c r="D190" t="n">
         <v>189</v>
@@ -3475,11 +3475,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LSC-49</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.7548875000535075</v>
+        <v>0.7280984159589723</v>
       </c>
       <c r="D191" t="n">
         <v>190</v>
@@ -3491,11 +3491,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.755283620274248</v>
+        <v>0.7281751381512649</v>
       </c>
       <c r="D192" t="n">
         <v>191</v>
@@ -3507,11 +3507,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DR-151</t>
+          <t>DR-34</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.7565779639736593</v>
+        <v>0.7282424741887771</v>
       </c>
       <c r="D193" t="n">
         <v>192</v>
@@ -3523,11 +3523,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DR-210</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.7565805411995415</v>
+        <v>0.7314550612108526</v>
       </c>
       <c r="D194" t="n">
         <v>193</v>
@@ -3539,11 +3539,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DR-154</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.7583025366794888</v>
+        <v>0.7323496818959766</v>
       </c>
       <c r="D195" t="n">
         <v>194</v>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SCR-03</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0.762404848086445</v>
+        <v>0.7330262701499582</v>
       </c>
       <c r="D196" t="n">
         <v>195</v>
@@ -3571,11 +3571,11 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.7646378735076567</v>
+        <v>0.7342350171989138</v>
       </c>
       <c r="D197" t="n">
         <v>196</v>
@@ -3587,11 +3587,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LSC-05</t>
+          <t>DR-67</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>0.7715062519803992</v>
+        <v>0.735155484170255</v>
       </c>
       <c r="D198" t="n">
         <v>197</v>
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>DR-82</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>0.7741729333826303</v>
+        <v>0.7378806387169611</v>
       </c>
       <c r="D199" t="n">
         <v>198</v>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>LSC-20</t>
+          <t>DR-69</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.7748574892518508</v>
+        <v>0.7379789416417593</v>
       </c>
       <c r="D200" t="n">
         <v>199</v>
@@ -3635,11 +3635,11 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DR-103</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.7761865256035769</v>
+        <v>0.740675667930827</v>
       </c>
       <c r="D201" t="n">
         <v>200</v>
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DR-149</t>
+          <t>DR-92</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.7829071532961724</v>
+        <v>0.7410414194799909</v>
       </c>
       <c r="D202" t="n">
         <v>201</v>
@@ -3667,11 +3667,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DR-146</t>
+          <t>DR-93</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0.7847547521283286</v>
+        <v>0.7425530444872658</v>
       </c>
       <c r="D203" t="n">
         <v>202</v>
@@ -3683,11 +3683,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DR-131</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>0.7901126219853953</v>
+        <v>0.7456988760153263</v>
       </c>
       <c r="D204" t="n">
         <v>203</v>
@@ -3699,11 +3699,11 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DR-216</t>
+          <t>DR-61</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.7927529410728149</v>
+        <v>0.750186914635289</v>
       </c>
       <c r="D205" t="n">
         <v>204</v>
@@ -3715,11 +3715,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DR-04</t>
+          <t>DR-234</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.7949238742549297</v>
+        <v>0.7507553489786106</v>
       </c>
       <c r="D206" t="n">
         <v>205</v>
@@ -3731,11 +3731,11 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DR-217</t>
+          <t>DR-78</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.8053803179439509</v>
+        <v>0.750917465912211</v>
       </c>
       <c r="D207" t="n">
         <v>206</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DR-190</t>
+          <t>DR-117</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.8057876058594206</v>
+        <v>0.751539898973878</v>
       </c>
       <c r="D208" t="n">
         <v>207</v>
@@ -3763,11 +3763,11 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DR-94</t>
+          <t>DR-147</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.8074827057650966</v>
+        <v>0.7515640193323273</v>
       </c>
       <c r="D209" t="n">
         <v>208</v>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>LSC-08</t>
+          <t>DR-154</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.8075787645323061</v>
+        <v>0.7518613990621861</v>
       </c>
       <c r="D210" t="n">
         <v>209</v>
@@ -3795,11 +3795,11 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DR-123</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.808120906612069</v>
+        <v>0.7529902992679407</v>
       </c>
       <c r="D211" t="n">
         <v>210</v>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DR-130</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.8085846529297001</v>
+        <v>0.753186116339721</v>
       </c>
       <c r="D212" t="n">
         <v>211</v>
@@ -3827,11 +3827,11 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>DR-136</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.8155236609032696</v>
+        <v>0.7535167462442788</v>
       </c>
       <c r="D213" t="n">
         <v>212</v>
@@ -3843,11 +3843,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>DR-170</t>
+          <t>DR-101</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.8168103052625093</v>
+        <v>0.7536542585767505</v>
       </c>
       <c r="D214" t="n">
         <v>213</v>
@@ -3859,11 +3859,11 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>LSC-13</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0.8170351109217519</v>
+        <v>0.7540690036122331</v>
       </c>
       <c r="D215" t="n">
         <v>214</v>
@@ -3875,11 +3875,11 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DR-88</t>
+          <t>DR-151</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0.8170891898991728</v>
+        <v>0.7564220104470806</v>
       </c>
       <c r="D216" t="n">
         <v>215</v>
@@ -3891,11 +3891,11 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DR-71</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>0.8173976154216486</v>
+        <v>0.7569137925221588</v>
       </c>
       <c r="D217" t="n">
         <v>216</v>
@@ -3907,11 +3907,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SCR-05</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.8179387607603645</v>
+        <v>0.7578316665799099</v>
       </c>
       <c r="D218" t="n">
         <v>217</v>
@@ -3923,11 +3923,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>DR-63</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.8187960522111127</v>
+        <v>0.7582948930217924</v>
       </c>
       <c r="D219" t="n">
         <v>218</v>
@@ -3939,11 +3939,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DR-121</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.8217537278579796</v>
+        <v>0.7587116391348507</v>
       </c>
       <c r="D220" t="n">
         <v>219</v>
@@ -3955,11 +3955,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>DR-108</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.8234933562974832</v>
+        <v>0.7606327737081996</v>
       </c>
       <c r="D221" t="n">
         <v>220</v>
@@ -3971,11 +3971,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DR-133</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0.8252447264562904</v>
+        <v>0.760853429796279</v>
       </c>
       <c r="D222" t="n">
         <v>221</v>
@@ -3987,11 +3987,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DR-95</t>
+          <t>DR-218</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.8257273107589458</v>
+        <v>0.7611866004872603</v>
       </c>
       <c r="D223" t="n">
         <v>222</v>
@@ -4003,11 +4003,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DR-109</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0.8276399801737792</v>
+        <v>0.7645745637160161</v>
       </c>
       <c r="D224" t="n">
         <v>223</v>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DR-137</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0.8292463579322019</v>
+        <v>0.7647321793134968</v>
       </c>
       <c r="D225" t="n">
         <v>224</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DR-126</t>
+          <t>DR-68</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0.8300937438114662</v>
+        <v>0.7656277566933765</v>
       </c>
       <c r="D226" t="n">
         <v>225</v>
@@ -4051,11 +4051,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DR-229</t>
+          <t>DR-114</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0.8318067580495626</v>
+        <v>0.7664369030417927</v>
       </c>
       <c r="D227" t="n">
         <v>226</v>
@@ -4067,11 +4067,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DR-129</t>
+          <t>DR-150</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>0.8323092860483637</v>
+        <v>0.766712684523832</v>
       </c>
       <c r="D228" t="n">
         <v>227</v>
@@ -4083,11 +4083,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DR-89</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>0.832417996810382</v>
+        <v>0.7672429171096496</v>
       </c>
       <c r="D229" t="n">
         <v>228</v>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DR-74</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>0.8331029990316078</v>
+        <v>0.7701780086237646</v>
       </c>
       <c r="D230" t="n">
         <v>229</v>
@@ -4115,11 +4115,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DR-112</t>
+          <t>DR-72</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.8342771037256772</v>
+        <v>0.7711920350115196</v>
       </c>
       <c r="D231" t="n">
         <v>230</v>
@@ -4131,11 +4131,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DR-127</t>
+          <t>DR-219</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>0.8367155983650418</v>
+        <v>0.7774016835589151</v>
       </c>
       <c r="D232" t="n">
         <v>231</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DR-100</t>
+          <t>DR-148</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>0.8368231194644373</v>
+        <v>0.7782476342307176</v>
       </c>
       <c r="D233" t="n">
         <v>232</v>
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>DR-85</t>
+          <t>DR-77</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>0.8388221221641986</v>
+        <v>0.7789247778934242</v>
       </c>
       <c r="D234" t="n">
         <v>233</v>
@@ -4179,11 +4179,11 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>DR-180</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>0.839265102285905</v>
+        <v>0.7795263846371498</v>
       </c>
       <c r="D235" t="n">
         <v>234</v>
@@ -4195,11 +4195,11 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>0.8405493901126285</v>
+        <v>0.7834952214761252</v>
       </c>
       <c r="D236" t="n">
         <v>235</v>
@@ -4211,11 +4211,11 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>DR-77</t>
+          <t>DR-91</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>0.8406595376757695</v>
+        <v>0.7875955683946494</v>
       </c>
       <c r="D237" t="n">
         <v>236</v>
@@ -4227,11 +4227,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DR-97</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>0.841367819168973</v>
+        <v>0.7879213543980511</v>
       </c>
       <c r="D238" t="n">
         <v>237</v>
@@ -4243,11 +4243,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DR-101</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0.8419619812886378</v>
+        <v>0.7885242646759798</v>
       </c>
       <c r="D239" t="n">
         <v>238</v>
@@ -4259,11 +4259,11 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DR-124</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>0.8432682668420505</v>
+        <v>0.789718471215767</v>
       </c>
       <c r="D240" t="n">
         <v>239</v>
@@ -4275,11 +4275,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>DR-60</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>0.8434316473042559</v>
+        <v>0.7925789163154541</v>
       </c>
       <c r="D241" t="n">
         <v>240</v>
@@ -4291,11 +4291,11 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>DR-184</t>
+          <t>DR-75</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>0.8435777400629513</v>
+        <v>0.7951828234446906</v>
       </c>
       <c r="D242" t="n">
         <v>241</v>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DR-139</t>
+          <t>DR-62</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>0.8435840614024143</v>
+        <v>0.7952576134313485</v>
       </c>
       <c r="D243" t="n">
         <v>242</v>
@@ -4323,11 +4323,11 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DR-107</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>0.8436844180598873</v>
+        <v>0.7974011336530248</v>
       </c>
       <c r="D244" t="n">
         <v>243</v>
@@ -4339,11 +4339,11 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>LSC-64</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>0.8453296883576514</v>
+        <v>0.7988479580359505</v>
       </c>
       <c r="D245" t="n">
         <v>244</v>
@@ -4355,11 +4355,11 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DR-83</t>
+          <t>DR-115</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>0.8461714672265884</v>
+        <v>0.8003113082856363</v>
       </c>
       <c r="D246" t="n">
         <v>245</v>
@@ -4371,11 +4371,11 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DR-75</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>0.8462693821907202</v>
+        <v>0.8008140943433474</v>
       </c>
       <c r="D247" t="n">
         <v>246</v>
@@ -4387,11 +4387,11 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>DR-93</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>0.8474154038557525</v>
+        <v>0.8024098501045118</v>
       </c>
       <c r="D248" t="n">
         <v>247</v>
@@ -4403,11 +4403,11 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DR-91</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>0.8475734038315531</v>
+        <v>0.8033445118844873</v>
       </c>
       <c r="D249" t="n">
         <v>248</v>
@@ -4419,11 +4419,11 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>DR-135</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>0.8500737697541936</v>
+        <v>0.8040945699688253</v>
       </c>
       <c r="D250" t="n">
         <v>249</v>
@@ -4435,11 +4435,11 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>DR-68</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>0.8501716975545801</v>
+        <v>0.8044506104338647</v>
       </c>
       <c r="D251" t="n">
         <v>250</v>
@@ -4451,11 +4451,11 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DR-96</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>0.8515926337888647</v>
+        <v>0.8050035501851058</v>
       </c>
       <c r="D252" t="n">
         <v>251</v>
@@ -4467,11 +4467,11 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>DR-86</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>0.8523789511894414</v>
+        <v>0.8064062453786458</v>
       </c>
       <c r="D253" t="n">
         <v>252</v>
@@ -4483,11 +4483,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>DR-105</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>0.8526764499528023</v>
+        <v>0.8068143048020595</v>
       </c>
       <c r="D254" t="n">
         <v>253</v>
@@ -4499,11 +4499,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DR-79</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>0.852779664356597</v>
+        <v>0.8106448722759528</v>
       </c>
       <c r="D255" t="n">
         <v>254</v>
@@ -4515,11 +4515,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DR-78</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>0.8543860196221917</v>
+        <v>0.8113569845756531</v>
       </c>
       <c r="D256" t="n">
         <v>255</v>
@@ -4531,11 +4531,11 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DR-99</t>
+          <t>DR-224</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>0.8550075123905827</v>
+        <v>0.8121079137427981</v>
       </c>
       <c r="D257" t="n">
         <v>256</v>
@@ -4547,11 +4547,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>DR-104</t>
+          <t>DR-124</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>0.8553907866032717</v>
+        <v>0.8146187503102864</v>
       </c>
       <c r="D258" t="n">
         <v>257</v>
@@ -4563,11 +4563,11 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DR-69</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>0.8558235024846439</v>
+        <v>0.8147013913534771</v>
       </c>
       <c r="D259" t="n">
         <v>258</v>
@@ -4579,11 +4579,11 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DR-61</t>
+          <t>DR-135</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>0.8569812492352644</v>
+        <v>0.8193244631787512</v>
       </c>
       <c r="D260" t="n">
         <v>259</v>
@@ -4595,11 +4595,11 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DR-110</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>0.8595283050724688</v>
+        <v>0.8195366475252188</v>
       </c>
       <c r="D261" t="n">
         <v>260</v>
@@ -4611,11 +4611,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DR-06</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>0.8597500425092688</v>
+        <v>0.8196995944975018</v>
       </c>
       <c r="D262" t="n">
         <v>261</v>
@@ -4627,11 +4627,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DR-72</t>
+          <t>DR-66</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>0.860134173182138</v>
+        <v>0.8203938056124732</v>
       </c>
       <c r="D263" t="n">
         <v>262</v>
@@ -4643,11 +4643,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DR-132</t>
+          <t>DR-81</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>0.8610267109979143</v>
+        <v>0.8234141555524372</v>
       </c>
       <c r="D264" t="n">
         <v>263</v>
@@ -4659,11 +4659,11 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DR-224</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>0.8624406032484547</v>
+        <v>0.8234527023448822</v>
       </c>
       <c r="D265" t="n">
         <v>264</v>
@@ -4675,11 +4675,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DR-58</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>0.8684353573915103</v>
+        <v>0.8240074651537562</v>
       </c>
       <c r="D266" t="n">
         <v>265</v>
@@ -4691,11 +4691,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DR-128</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>0.8701870204207891</v>
+        <v>0.8259340069048005</v>
       </c>
       <c r="D267" t="n">
         <v>266</v>
@@ -4707,11 +4707,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DR-218</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>0.8739169428533896</v>
+        <v>0.8262253997809225</v>
       </c>
       <c r="D268" t="n">
         <v>267</v>
@@ -4723,11 +4723,11 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DR-125</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>0.87501059591394</v>
+        <v>0.8272925730620532</v>
       </c>
       <c r="D269" t="n">
         <v>268</v>
@@ -4739,11 +4739,11 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DR-02</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>0.875428368862209</v>
+        <v>0.8295140664153087</v>
       </c>
       <c r="D270" t="n">
         <v>269</v>
@@ -4755,11 +4755,11 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DR-66</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>0.8767529786582693</v>
+        <v>0.8305532189535241</v>
       </c>
       <c r="D271" t="n">
         <v>270</v>
@@ -4771,11 +4771,11 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DR-117</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>0.878154107311422</v>
+        <v>0.8316697796530345</v>
       </c>
       <c r="D272" t="n">
         <v>271</v>
@@ -4787,11 +4787,11 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DR-134</t>
+          <t>DR-79</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>0.8781877825772471</v>
+        <v>0.8322452403365068</v>
       </c>
       <c r="D273" t="n">
         <v>272</v>
@@ -4803,11 +4803,11 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DR-67</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>0.8787512684729608</v>
+        <v>0.8338811444619408</v>
       </c>
       <c r="D274" t="n">
         <v>273</v>
@@ -4819,11 +4819,11 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DR-115</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>0.8840720227167302</v>
+        <v>0.8363603720932307</v>
       </c>
       <c r="D275" t="n">
         <v>274</v>
@@ -4835,11 +4835,11 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DR-116</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>0.8861454020522673</v>
+        <v>0.8440627997860608</v>
       </c>
       <c r="D276" t="n">
         <v>275</v>
@@ -4851,11 +4851,11 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DR-87</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>0.8865008629440071</v>
+        <v>0.8466118546548425</v>
       </c>
       <c r="D277" t="n">
         <v>276</v>
@@ -4867,11 +4867,11 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DR-07</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>0.8867706269128066</v>
+        <v>0.8468063652142074</v>
       </c>
       <c r="D278" t="n">
         <v>277</v>
@@ -4883,11 +4883,11 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DR-82</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>0.8910190354429394</v>
+        <v>0.8562199740202915</v>
       </c>
       <c r="D279" t="n">
         <v>278</v>
@@ -4899,11 +4899,11 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DR-219</t>
+          <t>DR-119</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>0.8918547235437025</v>
+        <v>0.8567069953533609</v>
       </c>
       <c r="D280" t="n">
         <v>279</v>
@@ -4915,11 +4915,11 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DR-13</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>0.8925394350711079</v>
+        <v>0.8614724371276922</v>
       </c>
       <c r="D281" t="n">
         <v>280</v>
@@ -4931,11 +4931,11 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DR-119</t>
+          <t>DR-06</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>0.8930400949016023</v>
+        <v>0.8633368572292847</v>
       </c>
       <c r="D282" t="n">
         <v>281</v>
@@ -4947,11 +4947,11 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DR-113</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>0.8943665637586663</v>
+        <v>0.8677316774292969</v>
       </c>
       <c r="D283" t="n">
         <v>282</v>
@@ -4963,11 +4963,11 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DR-102</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>0.896077374201509</v>
+        <v>0.8758341472155958</v>
       </c>
       <c r="D284" t="n">
         <v>283</v>
@@ -4979,11 +4979,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DR-46</t>
+          <t>LSC-64</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>0.8993842824057231</v>
+        <v>0.8789475407785508</v>
       </c>
       <c r="D285" t="n">
         <v>284</v>
@@ -4995,11 +4995,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DR-106</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>0.902094664955028</v>
+        <v>0.8846913122742949</v>
       </c>
       <c r="D286" t="n">
         <v>285</v>
@@ -5011,11 +5011,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DR-62</t>
+          <t>SCR-05</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>0.9023435681064832</v>
+        <v>0.8850898686990019</v>
       </c>
       <c r="D287" t="n">
         <v>286</v>
@@ -5027,11 +5027,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DR-122</t>
+          <t>DR-73</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>0.9066027348882969</v>
+        <v>0.8857791959035988</v>
       </c>
       <c r="D288" t="n">
         <v>287</v>
@@ -5043,11 +5043,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>LSC-21</t>
+          <t>DR-122</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>0.9076740501985733</v>
+        <v>0.887012500306678</v>
       </c>
       <c r="D289" t="n">
         <v>288</v>
@@ -5059,11 +5059,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DR-215</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>0.914736808914428</v>
+        <v>0.8920833878301081</v>
       </c>
       <c r="D290" t="n">
         <v>289</v>
@@ -5075,11 +5075,11 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DR-90</t>
+          <t>DR-70</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>0.9154981860236623</v>
+        <v>0.8941351709805596</v>
       </c>
       <c r="D291" t="n">
         <v>290</v>
@@ -5091,11 +5091,11 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>DR-161</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>0.915839719452416</v>
+        <v>0.8957125770611211</v>
       </c>
       <c r="D292" t="n">
         <v>291</v>
@@ -5107,11 +5107,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DR-211</t>
+          <t>DR-120</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>0.9204349152407724</v>
+        <v>0.9042671898228499</v>
       </c>
       <c r="D293" t="n">
         <v>292</v>
@@ -5123,11 +5123,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DR-60</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>0.9217139565678142</v>
+        <v>0.9061432992712449</v>
       </c>
       <c r="D294" t="n">
         <v>293</v>
@@ -5139,11 +5139,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DR-34</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>0.9246854244831948</v>
+        <v>0.9087020730030925</v>
       </c>
       <c r="D295" t="n">
         <v>294</v>
@@ -5155,11 +5155,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DR-92</t>
+          <t>DR-187</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>0.9252587478102722</v>
+        <v>0.920230912888681</v>
       </c>
       <c r="D296" t="n">
         <v>295</v>
@@ -5171,11 +5171,11 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DR-114</t>
+          <t>DR-138</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>0.9305019458373391</v>
+        <v>0.9233467544093091</v>
       </c>
       <c r="D297" t="n">
         <v>296</v>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>LSC-11</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>0.9418960625367413</v>
+        <v>0.9288136859530161</v>
       </c>
       <c r="D298" t="n">
         <v>297</v>
@@ -5203,11 +5203,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>DR-73</t>
+          <t>DR-80</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>0.9465494949833665</v>
+        <v>0.9296095673500351</v>
       </c>
       <c r="D299" t="n">
         <v>298</v>
@@ -5219,11 +5219,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>LSC-67</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>0.9470495324278043</v>
+        <v>0.9417891319721569</v>
       </c>
       <c r="D300" t="n">
         <v>299</v>
@@ -5235,11 +5235,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>DR-84</t>
+          <t>LSC-21</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>0.949082603135816</v>
+        <v>0.9471540499332677</v>
       </c>
       <c r="D301" t="n">
         <v>300</v>
@@ -5251,11 +5251,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>DR-81</t>
+          <t>LSC-67</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>0.950470872602708</v>
+        <v>0.9596175459553301</v>
       </c>
       <c r="D302" t="n">
         <v>301</v>
@@ -5267,11 +5267,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>DR-138</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>0.9584387621757808</v>
+        <v>0.9701106448055438</v>
       </c>
       <c r="D303" t="n">
         <v>302</v>
@@ -5283,11 +5283,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>DR-80</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>0.9631340526476359</v>
+        <v>0.9708357766492006</v>
       </c>
       <c r="D304" t="n">
         <v>303</v>
@@ -5299,11 +5299,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>DR-70</t>
+          <t>DR-84</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>0.9810530253169335</v>
+        <v>0.9882971456355734</v>
       </c>
       <c r="D305" t="n">
         <v>304</v>
@@ -5315,11 +5315,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DR-64</t>
+          <t>DR-111</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>0.9825899486763504</v>
+        <v>0.9959543301211721</v>
       </c>
       <c r="D306" t="n">
         <v>305</v>
@@ -5331,11 +5331,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DR-234</t>
+          <t>DR-64</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>0.9867629327403485</v>
+        <v>1</v>
       </c>
       <c r="D307" t="n">
         <v>306</v>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DR-118</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DR-111</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DR-187</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DR-120</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="C311" t="n">
